--- a/data/intermediate/fbkf.xlsx
+++ b/data/intermediate/fbkf.xlsx
@@ -31,19 +31,19 @@
     <t>Var. Mensual</t>
   </si>
   <si>
+    <t>Índice</t>
+  </si>
+  <si>
     <t>Var. Anual</t>
   </si>
   <si>
-    <t>Índice</t>
-  </si>
-  <si>
     <t>741103</t>
   </si>
   <si>
+    <t>741102</t>
+  </si>
+  <si>
     <t>741104</t>
-  </si>
-  <si>
-    <t>741102</t>
   </si>
   <si>
     <t>1993/02</t>
@@ -7203,10 +7203,10 @@
         <v>8</v>
       </c>
       <c r="C402" t="s">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="D402">
-        <v>14.3554919685408</v>
+        <v>54.5551565641348</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7217,10 +7217,10 @@
         <v>8</v>
       </c>
       <c r="C403" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D403">
-        <v>14.7744973087313</v>
+        <v>55.7277000024058</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7231,10 +7231,10 @@
         <v>8</v>
       </c>
       <c r="C404" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D404">
-        <v>16.7571593812949</v>
+        <v>56.4972565915955</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7245,10 +7245,10 @@
         <v>8</v>
       </c>
       <c r="C405" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D405">
-        <v>20.6712370807717</v>
+        <v>56.000165103122</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7259,10 +7259,10 @@
         <v>8</v>
       </c>
       <c r="C406" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D406">
-        <v>15.7262917682103</v>
+        <v>57.0623529372104</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7273,10 +7273,10 @@
         <v>8</v>
       </c>
       <c r="C407" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D407">
-        <v>20.7276393385768</v>
+        <v>54.9042665777449</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7287,10 +7287,10 @@
         <v>8</v>
       </c>
       <c r="C408" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D408">
-        <v>18.4282590064527</v>
+        <v>55.8380860676937</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7301,10 +7301,10 @@
         <v>8</v>
       </c>
       <c r="C409" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D409">
-        <v>16.1790424621263</v>
+        <v>57.3125001378712</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7315,10 +7315,10 @@
         <v>8</v>
       </c>
       <c r="C410" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D410">
-        <v>13.3746223150052</v>
+        <v>57.9233959877892</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7329,10 +7329,10 @@
         <v>8</v>
       </c>
       <c r="C411" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D411">
-        <v>12.4454866241616</v>
+        <v>59.2054917407515</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7343,10 +7343,10 @@
         <v>8</v>
       </c>
       <c r="C412" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D412">
-        <v>6.42118075664825</v>
+        <v>61.3075447264138</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7357,10 +7357,10 @@
         <v>8</v>
       </c>
       <c r="C413" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D413">
-        <v>-4.59387434239639</v>
+        <v>60.961176270989</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7371,10 +7371,10 @@
         <v>8</v>
       </c>
       <c r="C414" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D414">
-        <v>-17.8187115642401</v>
+        <v>62.386817683124</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7385,10 +7385,10 @@
         <v>8</v>
       </c>
       <c r="C415" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D415">
-        <v>-33.8044812312074</v>
+        <v>63.9611875394791</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7399,10 +7399,10 @@
         <v>8</v>
       </c>
       <c r="C416" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D416">
-        <v>-35.7638840905302</v>
+        <v>65.9645919247083</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7413,10 +7413,10 @@
         <v>8</v>
       </c>
       <c r="C417" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D417">
-        <v>-38.5725611187166</v>
+        <v>67.5760919972119</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7427,10 +7427,10 @@
         <v>8</v>
       </c>
       <c r="C418" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D418">
-        <v>-41.8155526470022</v>
+        <v>66.036145049922</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7441,10 +7441,10 @@
         <v>8</v>
       </c>
       <c r="C419" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D419">
-        <v>-39.4472406993659</v>
+        <v>66.2846249354706</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7455,10 +7455,10 @@
         <v>8</v>
       </c>
       <c r="C420" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D420">
-        <v>-38.994962187977</v>
+        <v>66.1280731924943</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7469,10 +7469,10 @@
         <v>8</v>
       </c>
       <c r="C421" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D421">
-        <v>-38.8181754214028</v>
+        <v>66.5851138712836</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7483,10 +7483,10 @@
         <v>8</v>
       </c>
       <c r="C422" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D422">
-        <v>-34.9067144366965</v>
+        <v>65.67043143318089</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7497,10 +7497,10 @@
         <v>8</v>
       </c>
       <c r="C423" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D423">
-        <v>-35.5717391579314</v>
+        <v>66.5739032961158</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7511,10 +7511,10 @@
         <v>8</v>
       </c>
       <c r="C424" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D424">
-        <v>-31.8099714000491</v>
+        <v>65.24421299075981</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7525,10 +7525,10 @@
         <v>8</v>
       </c>
       <c r="C425" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D425">
-        <v>-20.5430379763081</v>
+        <v>58.160696435453</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7539,10 +7539,10 @@
         <v>8</v>
       </c>
       <c r="C426" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D426">
-        <v>-8.21518542426502</v>
+        <v>51.2702905860598</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7553,10 +7553,10 @@
         <v>8</v>
       </c>
       <c r="C427" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D427">
-        <v>8.10614914081428</v>
+        <v>42.3394399024385</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7567,10 +7567,10 @@
         <v>8</v>
       </c>
       <c r="C428" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D428">
-        <v>9.391053284805389</v>
+        <v>42.3730917279644</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7581,10 +7581,10 @@
         <v>8</v>
       </c>
       <c r="C429" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D429">
-        <v>16.0453641633781</v>
+        <v>41.5102626099472</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7595,10 +7595,10 @@
         <v>8</v>
       </c>
       <c r="C430" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D430">
-        <v>27.646240164552</v>
+        <v>38.4227660505211</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7609,10 +7609,10 @@
         <v>8</v>
       </c>
       <c r="C431" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D431">
-        <v>26.4831174211065</v>
+        <v>40.1371693905036</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7623,10 +7623,10 @@
         <v>8</v>
       </c>
       <c r="C432" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D432">
-        <v>29.1499258142185</v>
+        <v>40.3414560554434</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7637,10 +7637,10 @@
         <v>8</v>
       </c>
       <c r="C433" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D433">
-        <v>27.8945957984718</v>
+        <v>40.7379875641879</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7651,10 +7651,10 @@
         <v>8</v>
       </c>
       <c r="C434" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D434">
-        <v>23.0844926494372</v>
+        <v>42.7470414634539</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7665,10 +7665,10 @@
         <v>8</v>
       </c>
       <c r="C435" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D435">
-        <v>26.3429443327699</v>
+        <v>42.892408068368</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7679,10 +7679,10 @@
         <v>8</v>
       </c>
       <c r="C436" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D436">
-        <v>21.1309115571221</v>
+        <v>44.490047498212</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7693,10 +7693,10 @@
         <v>8</v>
       </c>
       <c r="C437" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D437">
-        <v>19.7997937588598</v>
+        <v>46.2127224794326</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7707,10 +7707,10 @@
         <v>8</v>
       </c>
       <c r="C438" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D438">
-        <v>13.9493145847929</v>
+        <v>47.0583411468555</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7721,10 +7721,10 @@
         <v>8</v>
       </c>
       <c r="C439" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D439">
-        <v>18.6143415413554</v>
+        <v>45.7715380463156</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7735,10 +7735,10 @@
         <v>8</v>
       </c>
       <c r="C440" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D440">
-        <v>17.4017226394096</v>
+        <v>46.352371350557</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7749,10 +7749,10 @@
         <v>8</v>
       </c>
       <c r="C441" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D441">
-        <v>18.5879125311502</v>
+        <v>48.1707354108878</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7763,10 +7763,10 @@
         <v>8</v>
       </c>
       <c r="C442" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D442">
-        <v>18.5280356680031</v>
+        <v>49.0452162307121</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7777,10 +7777,10 @@
         <v>8</v>
       </c>
       <c r="C443" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D443">
-        <v>16.4528249657729</v>
+        <v>50.7667430896991</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7791,10 +7791,10 @@
         <v>8</v>
       </c>
       <c r="C444" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D444">
-        <v>13.9008066875539</v>
+        <v>52.1009605679807</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7805,10 +7805,10 @@
         <v>8</v>
       </c>
       <c r="C445" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D445">
-        <v>17.0654655494876</v>
+        <v>52.1016845316498</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7819,10 +7819,10 @@
         <v>8</v>
       </c>
       <c r="C446" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D446">
-        <v>15.0241145990528</v>
+        <v>52.6149791079368</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7833,10 +7833,10 @@
         <v>8</v>
       </c>
       <c r="C447" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D447">
-        <v>12.1555347398624</v>
+        <v>54.1915312488027</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7847,10 +7847,10 @@
         <v>8</v>
       </c>
       <c r="C448" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D448">
-        <v>16.4748499350296</v>
+        <v>53.8912000867808</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7861,10 +7861,10 @@
         <v>8</v>
       </c>
       <c r="C449" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D449">
-        <v>10.1011580574325</v>
+        <v>55.3627462207145</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7875,10 +7875,10 @@
         <v>8</v>
       </c>
       <c r="C450" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D450">
-        <v>13.4294033151327</v>
+        <v>53.6226571918154</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7889,10 +7889,10 @@
         <v>8</v>
       </c>
       <c r="C451" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D451">
-        <v>20.1372524435659</v>
+        <v>54.2916084669882</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7903,10 +7903,10 @@
         <v>8</v>
       </c>
       <c r="C452" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D452">
-        <v>21.6491574278532</v>
+        <v>54.4184824497701</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7917,10 +7917,10 @@
         <v>8</v>
       </c>
       <c r="C453" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D453">
-        <v>12.6807242345198</v>
+        <v>57.1246695746754</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7931,10 +7931,10 @@
         <v>8</v>
       </c>
       <c r="C454" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D454">
-        <v>15.0057937743981</v>
+        <v>58.1323313873877</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7945,10 +7945,10 @@
         <v>8</v>
       </c>
       <c r="C455" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D455">
-        <v>8.59796359203691</v>
+        <v>59.1193064710709</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7959,10 +7959,10 @@
         <v>8</v>
       </c>
       <c r="C456" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D456">
-        <v>9.86136730471663</v>
+        <v>59.3434143788944</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7973,10 +7973,10 @@
         <v>8</v>
       </c>
       <c r="C457" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D457">
-        <v>6.29659379717799</v>
+        <v>60.9930795561012</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7987,10 +7987,10 @@
         <v>8</v>
       </c>
       <c r="C458" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D458">
-        <v>9.54082700924423</v>
+        <v>60.5199138653809</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8001,10 +8001,10 @@
         <v>8</v>
       </c>
       <c r="C459" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D459">
-        <v>7.84364314809149</v>
+        <v>60.7788016558143</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8015,10 +8015,10 @@
         <v>8</v>
       </c>
       <c r="C460" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D460">
-        <v>2.33146511924791</v>
+        <v>62.7696944292645</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8029,10 +8029,10 @@
         <v>8</v>
       </c>
       <c r="C461" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D461">
-        <v>6.95869372771208</v>
+        <v>60.9550247214041</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8043,10 +8043,10 @@
         <v>8</v>
       </c>
       <c r="C462" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D462">
-        <v>10.5481367864924</v>
+        <v>60.8238600943953</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8057,10 +8057,10 @@
         <v>8</v>
       </c>
       <c r="C463" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D463">
-        <v>3.43568991573234</v>
+        <v>65.224446719658</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8071,10 +8071,10 @@
         <v>8</v>
       </c>
       <c r="C464" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D464">
-        <v>3.19867295134103</v>
+        <v>66.1996253851695</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8085,10 +8085,10 @@
         <v>8</v>
       </c>
       <c r="C465" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D465">
-        <v>4.89578926892111</v>
+        <v>64.3684913933206</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8099,10 +8099,10 @@
         <v>8</v>
       </c>
       <c r="C466" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D466">
-        <v>0.769700718330372</v>
+        <v>66.85554915162879</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8113,10 +8113,10 @@
         <v>8</v>
       </c>
       <c r="C467" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D467">
-        <v>5.96113596276507</v>
+        <v>64.2023629173183</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8127,10 +8127,10 @@
         <v>8</v>
       </c>
       <c r="C468" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D468">
-        <v>2.04679702756005</v>
+        <v>65.1954864419572</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8141,10 +8141,10 @@
         <v>8</v>
       </c>
       <c r="C469" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D469">
-        <v>3.88731616912149</v>
+        <v>64.83356602013851</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8155,10 +8155,10 @@
         <v>8</v>
       </c>
       <c r="C470" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D470">
-        <v>1.27556796971128</v>
+        <v>66.29401415342051</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8169,10 +8169,10 @@
         <v>8</v>
       </c>
       <c r="C471" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D471">
-        <v>3.38311868688639</v>
+        <v>65.5460739673827</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8183,10 +8183,10 @@
         <v>8</v>
       </c>
       <c r="C472" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D472">
-        <v>6.69099539357694</v>
+        <v>64.2331479603413</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8197,10 +8197,10 @@
         <v>8</v>
       </c>
       <c r="C473" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D473">
-        <v>7.36800388156156</v>
+        <v>65.1966982034178</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8211,10 +8211,10 @@
         <v>8</v>
       </c>
       <c r="C474" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D474">
-        <v>4.9078791950389</v>
+        <v>67.2396440559769</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8225,10 +8225,10 @@
         <v>8</v>
       </c>
       <c r="C475" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D475">
-        <v>4.87263910841467</v>
+        <v>67.4653564581975</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8239,10 +8239,10 @@
         <v>8</v>
       </c>
       <c r="C476" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D476">
-        <v>2.59464775680821</v>
+        <v>68.317134896254</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8253,10 +8253,10 @@
         <v>8</v>
       </c>
       <c r="C477" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D477">
-        <v>6.95012657337571</v>
+        <v>67.5198370875212</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8267,10 +8267,10 @@
         <v>8</v>
       </c>
       <c r="C478" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D478">
-        <v>6.4724546479887</v>
+        <v>67.37013679369259</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8281,10 +8281,10 @@
         <v>8</v>
       </c>
       <c r="C479" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D479">
-        <v>5.49150172202992</v>
+        <v>68.0295530621275</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8295,10 +8295,10 @@
         <v>8</v>
       </c>
       <c r="C480" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D480">
-        <v>8.17814594146769</v>
+        <v>66.5299057205545</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8309,10 +8309,10 @@
         <v>8</v>
       </c>
       <c r="C481" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D481">
-        <v>7.25668815386935</v>
+        <v>67.3538517150574</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8323,10 +8323,10 @@
         <v>8</v>
       </c>
       <c r="C482" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D482">
-        <v>5.71052354204118</v>
+        <v>67.1396393637974</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8337,10 +8337,10 @@
         <v>8</v>
       </c>
       <c r="C483" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D483">
-        <v>6.00621100834259</v>
+        <v>67.76357544429359</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8351,10 +8351,10 @@
         <v>8</v>
       </c>
       <c r="C484" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D484">
-        <v>3.01998189562148</v>
+        <v>68.5309849315172</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8365,10 +8365,10 @@
         <v>8</v>
       </c>
       <c r="C485" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D485">
-        <v>-2.12374823261434</v>
+        <v>70.00039345769559</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8379,10 +8379,10 @@
         <v>8</v>
       </c>
       <c r="C486" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D486">
-        <v>-3.92563631224868</v>
+        <v>70.5396845574184</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8393,10 +8393,10 @@
         <v>8</v>
       </c>
       <c r="C487" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D487">
-        <v>-5.14396785588956</v>
+        <v>70.752699801611</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8407,10 +8407,10 @@
         <v>8</v>
       </c>
       <c r="C488" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D488">
-        <v>-4.55382514992952</v>
+        <v>70.0897239043553</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="C489" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D489">
-        <v>-9.221560042226219</v>
+        <v>72.21255122724099</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8435,10 +8435,10 @@
         <v>8</v>
       </c>
       <c r="C490" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D490">
-        <v>-9.25903156521421</v>
+        <v>71.73063834395229</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8449,10 +8449,10 @@
         <v>8</v>
       </c>
       <c r="C491" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D491">
-        <v>-8.64840323714952</v>
+        <v>71.7653971400235</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8463,10 +8463,10 @@
         <v>8</v>
       </c>
       <c r="C492" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D492">
-        <v>-6.81510963207563</v>
+        <v>71.9708185051023</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8477,10 +8477,10 @@
         <v>8</v>
       </c>
       <c r="C493" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D493">
-        <v>-7.72266094883446</v>
+        <v>72.2415106936387</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8491,10 +8491,10 @@
         <v>8</v>
       </c>
       <c r="C494" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D494">
-        <v>-5.86799360789876</v>
+        <v>70.9736642757086</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8505,10 +8505,10 @@
         <v>8</v>
       </c>
       <c r="C495" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D495">
-        <v>-9.704819257176529</v>
+        <v>71.83359877227529</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8519,10 +8519,10 @@
         <v>8</v>
       </c>
       <c r="C496" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D496">
-        <v>-6.66561064866826</v>
+        <v>70.6006082693401</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8533,10 +8533,10 @@
         <v>8</v>
       </c>
       <c r="C497" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D497">
-        <v>-3.22531268356947</v>
+        <v>68.5137613388147</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8547,10 +8547,10 @@
         <v>8</v>
       </c>
       <c r="C498" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D498">
-        <v>-4.79759299832835</v>
+        <v>67.7705530858867</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8561,10 +8561,10 @@
         <v>8</v>
       </c>
       <c r="C499" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D499">
-        <v>-4.63902302961403</v>
+        <v>67.11320366664209</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8575,10 +8575,10 @@
         <v>8</v>
       </c>
       <c r="C500" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D500">
-        <v>-6.75956608478258</v>
+        <v>66.8979604296826</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8589,10 +8589,10 @@
         <v>8</v>
       </c>
       <c r="C501" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D501">
-        <v>-2.99588826817916</v>
+        <v>65.5534274577976</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8603,10 +8603,10 @@
         <v>8</v>
       </c>
       <c r="C502" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D502">
-        <v>-0.7269652356516469</v>
+        <v>65.0890758977561</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8617,10 +8617,10 @@
         <v>8</v>
       </c>
       <c r="C503" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D503">
-        <v>-2.35016069995532</v>
+        <v>65.5588362106125</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8631,10 +8631,10 @@
         <v>8</v>
       </c>
       <c r="C504" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D504">
-        <v>-3.31489749406696</v>
+        <v>67.0659283208774</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8645,10 +8645,10 @@
         <v>8</v>
       </c>
       <c r="C505" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D505">
-        <v>-2.47995592301857</v>
+        <v>66.662543758453</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8659,10 +8659,10 @@
         <v>8</v>
       </c>
       <c r="C506" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D506">
-        <v>-0.746294317176875</v>
+        <v>66.8089341927185</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8673,10 +8673,10 @@
         <v>8</v>
       </c>
       <c r="C507" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D507">
-        <v>1.66423382654881</v>
+        <v>64.8622778455006</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8687,10 +8687,10 @@
         <v>8</v>
       </c>
       <c r="C508" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D508">
-        <v>1.34981386569523</v>
+        <v>65.8946466065144</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8701,10 +8701,10 @@
         <v>8</v>
       </c>
       <c r="C509" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D509">
-        <v>-0.513251590152774</v>
+        <v>66.3039783043634</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8715,10 +8715,10 @@
         <v>8</v>
       </c>
       <c r="C510" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D510">
-        <v>2.20275107494926</v>
+        <v>64.51919777610981</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8729,10 +8729,10 @@
         <v>8</v>
       </c>
       <c r="C511" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D511">
-        <v>5.3708682734143</v>
+        <v>63.9998066926348</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8743,10 +8743,10 @@
         <v>8</v>
       </c>
       <c r="C512" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D512">
-        <v>5.97256604514903</v>
+        <v>62.3759485850665</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8757,10 +8757,10 @@
         <v>8</v>
       </c>
       <c r="C513" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D513">
-        <v>5.09618679990361</v>
+        <v>63.5895200152001</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8771,10 +8771,10 @@
         <v>8</v>
       </c>
       <c r="C514" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D514">
-        <v>1.95352997458553</v>
+        <v>64.6159009437725</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8785,10 +8785,10 @@
         <v>8</v>
       </c>
       <c r="C515" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D515">
-        <v>3.94102769058533</v>
+        <v>64.01809820664261</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8799,10 +8799,10 @@
         <v>8</v>
       </c>
       <c r="C516" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D516">
-        <v>2.38741829338929</v>
+        <v>64.8427615435959</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8813,10 +8813,10 @@
         <v>8</v>
       </c>
       <c r="C517" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D517">
-        <v>2.15601199090418</v>
+        <v>65.0093420560804</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8827,10 +8827,10 @@
         <v>8</v>
       </c>
       <c r="C518" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D518">
-        <v>-2.15469675939502</v>
+        <v>66.3103429134718</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8841,10 +8841,10 @@
         <v>8</v>
       </c>
       <c r="C519" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D519">
-        <v>-0.0448746789209971</v>
+        <v>65.94173781407549</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8855,10 +8855,10 @@
         <v>8</v>
       </c>
       <c r="C520" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D520">
-        <v>-2.85302788216353</v>
+        <v>66.78410168316</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8869,10 +8869,10 @@
         <v>8</v>
       </c>
       <c r="C521" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D521">
-        <v>0.256244830934605</v>
+        <v>65.9636720813817</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8883,10 +8883,10 @@
         <v>8</v>
       </c>
       <c r="C522" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D522">
-        <v>5.78978723520342</v>
+        <v>65.9403950986717</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8897,10 +8897,10 @@
         <v>8</v>
       </c>
       <c r="C523" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D523">
-        <v>1.65228962923914</v>
+        <v>67.437152005336</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8911,10 +8911,10 @@
         <v>8</v>
       </c>
       <c r="C524" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D524">
-        <v>6.00414983458767</v>
+        <v>66.1013933105978</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8925,10 +8925,10 @@
         <v>8</v>
       </c>
       <c r="C525" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D525">
-        <v>5.4591600696252</v>
+        <v>66.83016074033679</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8939,10 +8939,10 @@
         <v>8</v>
       </c>
       <c r="C526" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D526">
-        <v>6.75933094380821</v>
+        <v>65.87819193705759</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8953,10 +8953,10 @@
         <v>8</v>
       </c>
       <c r="C527" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D527">
-        <v>6.36469702155142</v>
+        <v>66.5410691839525</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8967,10 +8967,10 @@
         <v>8</v>
       </c>
       <c r="C528" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D528">
-        <v>5.77168742091727</v>
+        <v>66.3908294946265</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8981,10 +8981,10 @@
         <v>8</v>
       </c>
       <c r="C529" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D529">
-        <v>4.31619682413954</v>
+        <v>66.41095126601741</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8995,10 +8995,10 @@
         <v>8</v>
       </c>
       <c r="C530" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D530">
-        <v>7.90109079861929</v>
+        <v>64.8815561035715</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9009,10 +9009,10 @@
         <v>8</v>
       </c>
       <c r="C531" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D531">
-        <v>7.89269343911933</v>
+        <v>65.9121466709565</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9023,10 +9023,10 @@
         <v>8</v>
       </c>
       <c r="C532" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D532">
-        <v>10.4538668204043</v>
+        <v>64.878732641287</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9037,10 +9037,10 @@
         <v>8</v>
       </c>
       <c r="C533" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D533">
-        <v>8.173386027879211</v>
+        <v>66.1327005813849</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9051,10 +9051,10 @@
         <v>8</v>
       </c>
       <c r="C534" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D534">
-        <v>4.93468883908485</v>
+        <v>69.7582036769373</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9065,10 +9065,10 @@
         <v>8</v>
       </c>
       <c r="C535" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D535">
-        <v>4.78990841592843</v>
+        <v>68.5514090741744</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9079,10 +9079,10 @@
         <v>8</v>
       </c>
       <c r="C536" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D536">
-        <v>4.64780841743648</v>
+        <v>70.0702200077162</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9093,10 +9093,10 @@
         <v>8</v>
       </c>
       <c r="C537" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D537">
-        <v>1.99285493212454</v>
+        <v>70.4785261899396</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9107,10 +9107,10 @@
         <v>8</v>
       </c>
       <c r="C538" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D538">
-        <v>3.33413408398256</v>
+        <v>70.3311169498805</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9121,10 +9121,10 @@
         <v>8</v>
       </c>
       <c r="C539" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D539">
-        <v>3.2870027964213</v>
+        <v>70.776206632412</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9135,10 +9135,10 @@
         <v>8</v>
       </c>
       <c r="C540" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D540">
-        <v>3.1971623011388</v>
+        <v>70.22270064921049</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9149,10 +9149,10 @@
         <v>8</v>
       </c>
       <c r="C541" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D541">
-        <v>6.27701656341957</v>
+        <v>69.2773786354421</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9163,10 +9163,10 @@
         <v>8</v>
       </c>
       <c r="C542" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D542">
-        <v>6.09466977303418</v>
+        <v>70.0079067628718</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9177,10 +9177,10 @@
         <v>8</v>
       </c>
       <c r="C543" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D543">
-        <v>4.86239960762255</v>
+        <v>71.11439034683779</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9191,10 +9191,10 @@
         <v>8</v>
       </c>
       <c r="C544" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D544">
-        <v>7.21801292760101</v>
+        <v>71.66106894637331</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9205,10 +9205,10 @@
         <v>8</v>
       </c>
       <c r="C545" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D545">
-        <v>8.81878980741725</v>
+        <v>71.537981490563</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9219,10 +9219,10 @@
         <v>8</v>
       </c>
       <c r="C546" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D546">
-        <v>7.50125029423277</v>
+        <v>73.2005539681292</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9233,10 +9233,10 @@
         <v>8</v>
       </c>
       <c r="C547" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D547">
-        <v>8.27848344949367</v>
+        <v>71.8349587866558</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9247,10 +9247,10 @@
         <v>8</v>
       </c>
       <c r="C548" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D548">
-        <v>8.69321387486365</v>
+        <v>73.3269495913511</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9261,10 +9261,10 @@
         <v>8</v>
       </c>
       <c r="C549" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D549">
-        <v>11.9094821876158</v>
+        <v>71.8830609752045</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9275,10 +9275,10 @@
         <v>8</v>
       </c>
       <c r="C550" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D550">
-        <v>11.0839267339569</v>
+        <v>72.6760506917521</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9289,10 +9289,10 @@
         <v>8</v>
       </c>
       <c r="C551" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D551">
-        <v>10.2118506706927</v>
+        <v>73.1026225236203</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9303,10 +9303,10 @@
         <v>8</v>
       </c>
       <c r="C552" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D552">
-        <v>11.9861432133522</v>
+        <v>72.4678343612086</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9317,10 +9317,10 @@
         <v>8</v>
       </c>
       <c r="C553" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D553">
-        <v>12.1581885054312</v>
+        <v>73.62593116709169</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9331,10 +9331,10 @@
         <v>8</v>
       </c>
       <c r="C554" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D554">
-        <v>12.3192369806352</v>
+        <v>74.27465749508249</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9345,10 +9345,10 @@
         <v>8</v>
       </c>
       <c r="C555" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D555">
-        <v>10.305048308508</v>
+        <v>74.5722561840256</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9359,10 +9359,10 @@
         <v>8</v>
       </c>
       <c r="C556" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D556">
-        <v>7.3207529722395</v>
+        <v>76.8335741669796</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9373,10 +9373,10 @@
         <v>8</v>
       </c>
       <c r="C557" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D557">
-        <v>6.9599298853412</v>
+        <v>77.84676571068481</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9387,10 +9387,10 @@
         <v>8</v>
       </c>
       <c r="C558" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D558">
-        <v>3.23272081391438</v>
+        <v>78.6915107380435</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9401,10 +9401,10 @@
         <v>8</v>
       </c>
       <c r="C559" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D559">
-        <v>7.01404005330068</v>
+        <v>77.7818039607597</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9415,10 +9415,10 @@
         <v>8</v>
       </c>
       <c r="C560" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D560">
-        <v>4.96643690450474</v>
+        <v>79.7014181472407</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9429,10 +9429,10 @@
         <v>8</v>
       </c>
       <c r="C561" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D561">
-        <v>5.59044563945445</v>
+        <v>80.44396131795951</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9443,10 +9443,10 @@
         <v>8</v>
       </c>
       <c r="C562" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D562">
-        <v>5.45126053811167</v>
+        <v>80.73141090355929</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9457,10 +9457,10 @@
         <v>8</v>
       </c>
       <c r="C563" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D563">
-        <v>3.75197751303692</v>
+        <v>80.56775317209259</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9471,10 +9471,10 @@
         <v>8</v>
       </c>
       <c r="C564" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D564">
-        <v>6.89905148859247</v>
+        <v>81.1539327713579</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9485,10 +9485,10 @@
         <v>8</v>
       </c>
       <c r="C565" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D565">
-        <v>6.30065790175675</v>
+        <v>82.5775106672657</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9499,10 +9499,10 @@
         <v>8</v>
       </c>
       <c r="C566" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D566">
-        <v>11.1075768798166</v>
+        <v>83.4247285684568</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9513,10 +9513,10 @@
         <v>8</v>
       </c>
       <c r="C567" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D567">
-        <v>9.9174277872029</v>
+        <v>82.2569632085338</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9527,10 +9527,10 @@
         <v>8</v>
       </c>
       <c r="C568" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D568">
-        <v>10.3142262400887</v>
+        <v>82.45837033148661</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9541,10 +9541,10 @@
         <v>8</v>
       </c>
       <c r="C569" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D569">
-        <v>8.74260713871762</v>
+        <v>83.2648460221543</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9555,10 +9555,10 @@
         <v>8</v>
       </c>
       <c r="C570" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D570">
-        <v>13.2328554602591</v>
+        <v>81.23538758445591</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9569,10 +9569,10 @@
         <v>8</v>
       </c>
       <c r="C571" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D571">
-        <v>13.2073611256825</v>
+        <v>83.2374508447472</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9583,10 +9583,10 @@
         <v>8</v>
       </c>
       <c r="C572" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D572">
-        <v>10.5008578096117</v>
+        <v>83.6597387915189</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9597,10 +9597,10 @@
         <v>8</v>
       </c>
       <c r="C573" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D573">
-        <v>9.510529725028849</v>
+        <v>84.9411372456638</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9611,10 +9611,10 @@
         <v>8</v>
       </c>
       <c r="C574" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D574">
-        <v>11.7047216528158</v>
+        <v>85.1322904480058</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9625,10 +9625,10 @@
         <v>8</v>
       </c>
       <c r="C575" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D575">
-        <v>15.0624301658456</v>
+        <v>83.5906371538686</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9639,10 +9639,10 @@
         <v>8</v>
       </c>
       <c r="C576" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D576">
-        <v>12.6221401107915</v>
+        <v>86.7527843782716</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9653,10 +9653,10 @@
         <v>8</v>
       </c>
       <c r="C577" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D577">
-        <v>5.84129007279627</v>
+        <v>87.7804371181968</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9667,10 +9667,10 @@
         <v>8</v>
       </c>
       <c r="C578" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D578">
-        <v>-1.75651985669449</v>
+        <v>92.69119443097649</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9681,10 +9681,10 @@
         <v>8</v>
       </c>
       <c r="C579" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D579">
-        <v>0.880549811261759</v>
+        <v>90.4147381346862</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9695,10 +9695,10 @@
         <v>8</v>
       </c>
       <c r="C580" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D580">
-        <v>-1.32833501646481</v>
+        <v>90.9633132013663</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9709,10 +9709,10 @@
         <v>8</v>
       </c>
       <c r="C581" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D581">
-        <v>-5.36323517737168</v>
+        <v>90.5443643945294</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9723,10 +9723,10 @@
         <v>8</v>
       </c>
       <c r="C582" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D582">
-        <v>-11.2526966593273</v>
+        <v>91.98514900608821</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9737,10 +9737,10 @@
         <v>8</v>
       </c>
       <c r="C583" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D583">
-        <v>-14.0578552100779</v>
+        <v>94.23092156962539</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9751,10 +9751,10 @@
         <v>8</v>
       </c>
       <c r="C584" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D584">
-        <v>-12.6553514463911</v>
+        <v>92.4447290059089</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9765,10 +9765,10 @@
         <v>8</v>
       </c>
       <c r="C585" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D585">
-        <v>-13.831405847913</v>
+        <v>93.01948935219021</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9779,10 +9779,10 @@
         <v>8</v>
       </c>
       <c r="C586" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D586">
-        <v>-15.5456768269914</v>
+        <v>95.09678808161161</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9793,10 +9793,10 @@
         <v>8</v>
       </c>
       <c r="C587" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D587">
-        <v>-15.3067013791318</v>
+        <v>96.18141850035541</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9807,10 +9807,10 @@
         <v>8</v>
       </c>
       <c r="C588" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D588">
-        <v>-15.040704963837</v>
+        <v>97.70284237250991</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9821,10 +9821,10 @@
         <v>8</v>
       </c>
       <c r="C589" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D589">
-        <v>-12.7254217976555</v>
+        <v>92.9079470774392</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="C590" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D590">
-        <v>-9.9402513088753</v>
+        <v>91.0630551953891</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9849,10 +9849,10 @@
         <v>8</v>
       </c>
       <c r="C591" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D591">
-        <v>-10.6191886452156</v>
+        <v>91.210884940684</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9863,10 +9863,10 @@
         <v>8</v>
       </c>
       <c r="C592" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D592">
-        <v>-9.397974497816429</v>
+        <v>89.755015659976</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9877,10 +9877,10 @@
         <v>8</v>
       </c>
       <c r="C593" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D593">
-        <v>-2.92031088213736</v>
+        <v>85.6882571921944</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9891,10 +9891,10 @@
         <v>8</v>
       </c>
       <c r="C594" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D594">
-        <v>3.3148078072714</v>
+        <v>81.6343392168029</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9905,10 +9905,10 @@
         <v>8</v>
       </c>
       <c r="C595" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D595">
-        <v>3.50876242639696</v>
+        <v>80.9840750522454</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9919,10 +9919,10 @@
         <v>8</v>
       </c>
       <c r="C596" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D596">
-        <v>6.62074723569078</v>
+        <v>80.74552365654731</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9933,10 +9933,10 @@
         <v>8</v>
       </c>
       <c r="C597" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D597">
-        <v>8.78299328190249</v>
+        <v>80.15358626223259</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9947,10 +9947,10 @@
         <v>8</v>
       </c>
       <c r="C598" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D598">
-        <v>6.26829192375456</v>
+        <v>80.3133487335954</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9961,10 +9961,10 @@
         <v>8</v>
       </c>
       <c r="C599" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D599">
-        <v>5.47584878534561</v>
+        <v>81.459215988293</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -9975,10 +9975,10 @@
         <v>8</v>
       </c>
       <c r="C600" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D600">
-        <v>1.44771136261898</v>
+        <v>83.007646109978</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -9989,10 +9989,10 @@
         <v>8</v>
       </c>
       <c r="C601" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D601">
-        <v>6.21319938666147</v>
+        <v>81.0850189282925</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -10003,10 +10003,10 @@
         <v>8</v>
       </c>
       <c r="C602" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D602">
-        <v>6.15881221365719</v>
+        <v>82.01115865942759</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10017,10 +10017,10 @@
         <v>8</v>
       </c>
       <c r="C603" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D603">
-        <v>8.26760056596825</v>
+        <v>81.5250290038622</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10031,10 +10031,10 @@
         <v>8</v>
       </c>
       <c r="C604" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D604">
-        <v>8.79884736182705</v>
+        <v>81.3198621777403</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -10045,10 +10045,10 @@
         <v>8</v>
       </c>
       <c r="C605" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D605">
-        <v>7.50723290921988</v>
+        <v>83.18589369269689</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10059,10 +10059,10 @@
         <v>8</v>
       </c>
       <c r="C606" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="D606">
-        <v>8.14854079784979</v>
+        <v>84.3403606665759</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -10073,10 +10073,10 @@
         <v>8</v>
       </c>
       <c r="C607" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="D607">
-        <v>6.11103183097494</v>
+        <v>83.82561384904371</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10087,10 +10087,10 @@
         <v>8</v>
       </c>
       <c r="C608" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D608">
-        <v>2.73309800164529</v>
+        <v>86.0914806819822</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -10101,10 +10101,10 @@
         <v>8</v>
       </c>
       <c r="C609" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D609">
-        <v>2.94433990661627</v>
+        <v>87.1934703588484</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10115,10 +10115,10 @@
         <v>8</v>
       </c>
       <c r="C610" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D610">
-        <v>8.129054790105171</v>
+        <v>85.3476238859602</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -10129,10 +10129,10 @@
         <v>8</v>
       </c>
       <c r="C611" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D611">
-        <v>11.4722936086182</v>
+        <v>85.91979947754</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10143,10 +10143,10 @@
         <v>8</v>
       </c>
       <c r="C612" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D612">
-        <v>12.3884928902715</v>
+        <v>84.2093572345547</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -10157,10 +10157,10 @@
         <v>8</v>
       </c>
       <c r="C613" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D613">
-        <v>12.3489582388524</v>
+        <v>86.1229928270195</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -10171,10 +10171,10 @@
         <v>8</v>
       </c>
       <c r="C614" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D614">
-        <v>8.69837425506643</v>
+        <v>87.06207191550619</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -10185,10 +10185,10 @@
         <v>8</v>
       </c>
       <c r="C615" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D615">
-        <v>9.40297631833521</v>
+        <v>88.26519276319129</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -10199,10 +10199,10 @@
         <v>8</v>
       </c>
       <c r="C616" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D616">
-        <v>10.0609433525706</v>
+        <v>88.4750727256078</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -10213,10 +10213,10 @@
         <v>8</v>
       </c>
       <c r="C617" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="D617">
-        <v>10.5724356733869</v>
+        <v>89.4308524798237</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -10227,10 +10227,10 @@
         <v>8</v>
       </c>
       <c r="C618" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D618">
-        <v>6.23806897414487</v>
+        <v>91.2128693645455</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -10241,10 +10241,10 @@
         <v>8</v>
       </c>
       <c r="C619" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D619">
-        <v>9.191377571648969</v>
+        <v>88.94822379386891</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -10255,10 +10255,10 @@
         <v>8</v>
       </c>
       <c r="C620" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="D620">
-        <v>8.912204661196631</v>
+        <v>88.4444452200883</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -10269,10 +10269,10 @@
         <v>8</v>
       </c>
       <c r="C621" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D621">
-        <v>9.94266362716966</v>
+        <v>89.7607425025876</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -10283,10 +10283,10 @@
         <v>8</v>
       </c>
       <c r="C622" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D622">
-        <v>6.28576421104366</v>
+        <v>92.2855789937028</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -10297,10 +10297,10 @@
         <v>8</v>
       </c>
       <c r="C623" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D623">
-        <v>0.779083562130314</v>
+        <v>95.7767711415394</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -10311,10 +10311,10 @@
         <v>8</v>
       </c>
       <c r="C624" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D624">
-        <v>5.24164725673434</v>
+        <v>94.6416274685008</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -10325,10 +10325,10 @@
         <v>8</v>
       </c>
       <c r="C625" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D625">
-        <v>0.542841241839629</v>
+        <v>96.758285245278</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -10339,10 +10339,10 @@
         <v>8</v>
       </c>
       <c r="C626" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D626">
-        <v>5.23457036192274</v>
+        <v>94.635056764932</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -10353,10 +10353,10 @@
         <v>8</v>
       </c>
       <c r="C627" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D627">
-        <v>0.517414672287457</v>
+        <v>96.5647479360471</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -10367,10 +10367,10 @@
         <v>8</v>
       </c>
       <c r="C628" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D628">
-        <v>0.761394282581225</v>
+        <v>97.3764996736768</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -10381,10 +10381,10 @@
         <v>8</v>
       </c>
       <c r="C629" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D629">
-        <v>-4.66440490877731</v>
+        <v>98.8858718304146</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -10395,10 +10395,10 @@
         <v>8</v>
       </c>
       <c r="C630" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D630">
-        <v>-2.31422504087096</v>
+        <v>96.9027910688025</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -10409,10 +10409,10 @@
         <v>8</v>
       </c>
       <c r="C631" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D631">
-        <v>-0.138697705022205</v>
+        <v>97.12379088603871</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -10423,10 +10423,10 @@
         <v>8</v>
       </c>
       <c r="C632" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D632">
-        <v>-0.00343298827807071</v>
+        <v>96.3267951895625</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -10437,10 +10437,10 @@
         <v>8</v>
       </c>
       <c r="C633" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D633">
-        <v>-5.29392050500696</v>
+        <v>98.6853511988698</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -10451,10 +10451,10 @@
         <v>8</v>
       </c>
       <c r="C634" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D634">
-        <v>-3.07901082688313</v>
+        <v>98.0864328900434</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -10465,10 +10465,10 @@
         <v>8</v>
       </c>
       <c r="C635" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D635">
-        <v>-4.92163143633914</v>
+        <v>96.5229522218423</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -10479,10 +10479,10 @@
         <v>8</v>
       </c>
       <c r="C636" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D636">
-        <v>-5.8986507499456</v>
+        <v>99.60240773843221</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -10493,10 +10493,10 @@
         <v>8</v>
       </c>
       <c r="C637" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D637">
-        <v>-5.66577665791175</v>
+        <v>97.2835291224862</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -10507,10 +10507,10 @@
         <v>8</v>
       </c>
       <c r="C638" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D638">
-        <v>-8.042713982884329</v>
+        <v>99.58879539833789</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -10521,10 +10521,10 @@
         <v>8</v>
       </c>
       <c r="C639" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D639">
-        <v>-5.25893268869636</v>
+        <v>97.06438811012561</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -10535,10 +10535,10 @@
         <v>8</v>
       </c>
       <c r="C640" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D640">
-        <v>-7.25727842001518</v>
+        <v>98.1179187747699</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -10549,10 +10549,10 @@
         <v>8</v>
       </c>
       <c r="C641" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D641">
-        <v>-0.374332693904586</v>
+        <v>94.27343437066951</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -10563,10 +10563,10 @@
         <v>8</v>
       </c>
       <c r="C642" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D642">
-        <v>-3.10226105659441</v>
+        <v>94.6602424125854</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -10577,10 +10577,10 @@
         <v>8</v>
       </c>
       <c r="C643" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D643">
-        <v>-2.39757981971055</v>
+        <v>96.9890824170492</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -10591,10 +10591,10 @@
         <v>8</v>
       </c>
       <c r="C644" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D644">
-        <v>-0.789527112603348</v>
+        <v>96.323488301975</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -10605,10 +10605,10 @@
         <v>8</v>
       </c>
       <c r="C645" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D645">
-        <v>2.18976393454287</v>
+        <v>93.4610271563147</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -10619,10 +10619,10 @@
         <v>8</v>
       </c>
       <c r="C646" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D646">
-        <v>0.163570141979586</v>
+        <v>95.0663410016555</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -10633,10 +10633,10 @@
         <v>8</v>
       </c>
       <c r="C647" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D647">
-        <v>4.3047401565426</v>
+        <v>91.7724482620095</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -10647,10 +10647,10 @@
         <v>8</v>
       </c>
       <c r="C648" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D648">
-        <v>0.596195224031533</v>
+        <v>93.7272095674053</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -10661,10 +10661,10 @@
         <v>8</v>
       </c>
       <c r="C649" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D649">
-        <v>4.06049020457768</v>
+        <v>91.7716616374716</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -10675,10 +10675,10 @@
         <v>8</v>
       </c>
       <c r="C650" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D650">
-        <v>3.25446477634094</v>
+        <v>91.5791534254497</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -10689,10 +10689,10 @@
         <v>8</v>
       </c>
       <c r="C651" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D651">
-        <v>7.60240757909002</v>
+        <v>91.95983727471911</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -10703,10 +10703,10 @@
         <v>8</v>
       </c>
       <c r="C652" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D652">
-        <v>7.97795626437392</v>
+        <v>90.9972282293605</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -10717,10 +10717,10 @@
         <v>8</v>
       </c>
       <c r="C653" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D653">
-        <v>4.28827104538591</v>
+        <v>93.92053808415341</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -10731,10 +10731,10 @@
         <v>8</v>
       </c>
       <c r="C654" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D654">
-        <v>8.104159694967541</v>
+        <v>91.7236345761419</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -10745,10 +10745,10 @@
         <v>8</v>
       </c>
       <c r="C655" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D655">
-        <v>1.58978763755633</v>
+        <v>94.6636917496956</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -10759,10 +10759,10 @@
         <v>8</v>
       </c>
       <c r="C656" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D656">
-        <v>1.7273954945926</v>
+        <v>95.5629882460256</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -10773,10 +10773,10 @@
         <v>8</v>
       </c>
       <c r="C657" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D657">
-        <v>5.49265836773285</v>
+        <v>95.507603021837</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -10787,10 +10787,10 @@
         <v>8</v>
       </c>
       <c r="C658" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D658">
-        <v>3.60182141639648</v>
+        <v>95.22184115060671</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -10801,10 +10801,10 @@
         <v>8</v>
       </c>
       <c r="C659" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D659">
-        <v>5.316250560657</v>
+        <v>95.72301369498651</v>
       </c>
     </row>
     <row r="660" spans="1:4">
@@ -10815,10 +10815,10 @@
         <v>8</v>
       </c>
       <c r="C660" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D660">
-        <v>8.925553390212469</v>
+        <v>94.28600671446419</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -10829,10 +10829,10 @@
         <v>8</v>
       </c>
       <c r="C661" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D661">
-        <v>7.0193360725305</v>
+        <v>95.49804096883931</v>
       </c>
     </row>
     <row r="662" spans="1:4">
@@ -10843,10 +10843,10 @@
         <v>8</v>
       </c>
       <c r="C662" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D662">
-        <v>9.270151666706511</v>
+        <v>94.5595647161522</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -10857,10 +10857,10 @@
         <v>8</v>
       </c>
       <c r="C663" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D663">
-        <v>0.800510939235751</v>
+        <v>98.9509989134112</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -10871,10 +10871,10 @@
         <v>8</v>
       </c>
       <c r="C664" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D664">
-        <v>2.76747952970163</v>
+        <v>98.2569472992914</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -10885,10 +10885,10 @@
         <v>8</v>
       </c>
       <c r="C665" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="D665">
-        <v>0.756592567293626</v>
+        <v>97.9481053244868</v>
       </c>
     </row>
     <row r="666" spans="1:4">
@@ -10899,10 +10899,10 @@
         <v>8</v>
       </c>
       <c r="C666" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="D666">
-        <v>0.274660540972504</v>
+        <v>99.1570644002209</v>
       </c>
     </row>
     <row r="667" spans="1:4">
@@ -10913,10 +10913,10 @@
         <v>8</v>
       </c>
       <c r="C667" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D667">
-        <v>5.34587560590605</v>
+        <v>96.16864341838669</v>
       </c>
     </row>
     <row r="668" spans="1:4">
@@ -10927,10 +10927,10 @@
         <v>8</v>
       </c>
       <c r="C668" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D668">
-        <v>2.56784680888738</v>
+        <v>97.2137389994855</v>
       </c>
     </row>
     <row r="669" spans="1:4">
@@ -10941,10 +10941,10 @@
         <v>8</v>
       </c>
       <c r="C669" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D669">
-        <v>-0.930562546067117</v>
+        <v>100.753509371037</v>
       </c>
     </row>
     <row r="670" spans="1:4">
@@ -10955,10 +10955,10 @@
         <v>8</v>
       </c>
       <c r="C670" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="D670">
-        <v>0.0439500513345879</v>
+        <v>98.6515618182563</v>
       </c>
     </row>
     <row r="671" spans="1:4">
@@ -10969,10 +10969,10 @@
         <v>8</v>
       </c>
       <c r="C671" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D671">
-        <v>-1.52524180854429</v>
+        <v>100.811888947224</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -10983,10 +10983,10 @@
         <v>8</v>
       </c>
       <c r="C672" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D672">
-        <v>-5.06938934402349</v>
+        <v>102.701554583263</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -10997,10 +10997,10 @@
         <v>8</v>
       </c>
       <c r="C673" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D673">
-        <v>-1.43808279254283</v>
+        <v>102.201369407125</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -11011,10 +11011,10 @@
         <v>8</v>
       </c>
       <c r="C674" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D674">
-        <v>-2.76129252858498</v>
+        <v>103.325379780717</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -11025,10 +11025,10 @@
         <v>8</v>
       </c>
       <c r="C675" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D675">
-        <v>2.01763156424236</v>
+        <v>99.7431124841961</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -11039,10 +11039,10 @@
         <v>8</v>
       </c>
       <c r="C676" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="D676">
-        <v>2.13939306695041</v>
+        <v>100.976188202309</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -11053,10 +11053,10 @@
         <v>8</v>
       </c>
       <c r="C677" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="D677">
-        <v>4.20413143011328</v>
+        <v>98.6891734091768</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -11067,10 +11067,10 @@
         <v>8</v>
       </c>
       <c r="C678" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D678">
-        <v>1.46555623478724</v>
+        <v>99.429409729715</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -11081,10 +11081,10 @@
         <v>8</v>
       </c>
       <c r="C679" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D679">
-        <v>-1.823076646005</v>
+        <v>101.309699467421</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -11095,10 +11095,10 @@
         <v>8</v>
       </c>
       <c r="C680" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D680">
-        <v>0.717637655961084</v>
+        <v>99.7100388941839</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -11109,10 +11109,10 @@
         <v>8</v>
       </c>
       <c r="C681" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D681">
-        <v>-2.54125818252678</v>
+        <v>99.8159349489819</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -11123,10 +11123,10 @@
         <v>8</v>
       </c>
       <c r="C682" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="D682">
-        <v>0.962925186517172</v>
+        <v>98.69491923031779</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -11137,10 +11137,10 @@
         <v>8</v>
       </c>
       <c r="C683" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D683">
-        <v>1.21956752405005</v>
+        <v>99.2742638690177</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -11151,10 +11151,10 @@
         <v>8</v>
       </c>
       <c r="C684" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D684">
-        <v>1.72687846494691</v>
+        <v>97.4952129190726</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -11165,10 +11165,10 @@
         <v>8</v>
       </c>
       <c r="C685" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D685">
-        <v>-0.624029896061112</v>
+        <v>100.731629099938</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -11179,10 +11179,10 @@
         <v>8</v>
       </c>
       <c r="C686" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="D686">
-        <v>-0.492605041705924</v>
+        <v>100.4722637887</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -11193,10 +11193,10 @@
         <v>8</v>
       </c>
       <c r="C687" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D687">
-        <v>-2.22540993316464</v>
+        <v>101.755561004835</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -11207,10 +11207,10 @@
         <v>8</v>
       </c>
       <c r="C688" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="D688">
-        <v>-3.53148277205967</v>
+        <v>103.13646577198</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -11221,10 +11221,10 @@
         <v>8</v>
       </c>
       <c r="C689" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D689">
-        <v>-0.18111508934143</v>
+        <v>102.838195966591</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -11235,10 +11235,10 @@
         <v>8</v>
       </c>
       <c r="C690" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D690">
-        <v>-0.448329840236811</v>
+        <v>100.886603643221</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="C691" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D691">
-        <v>2.10179933195925</v>
+        <v>99.4627459962926</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -11263,10 +11263,10 @@
         <v>8</v>
       </c>
       <c r="C692" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D692">
-        <v>1.59477647430073</v>
+        <v>100.425595680062</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -11277,10 +11277,10 @@
         <v>8</v>
       </c>
       <c r="C693" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="D693">
-        <v>2.93936577946524</v>
+        <v>97.2793543346253</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -11291,10 +11291,10 @@
         <v>8</v>
       </c>
       <c r="C694" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="D694">
-        <v>2.62023418961858</v>
+        <v>99.6452774653993</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -11305,10 +11305,10 @@
         <v>8</v>
       </c>
       <c r="C695" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D695">
-        <v>1.40156843433387</v>
+        <v>100.484980550904</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -11319,10 +11319,10 @@
         <v>8</v>
       </c>
       <c r="C696" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D696">
-        <v>3.40639226929062</v>
+        <v>99.1788367553262</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -11333,10 +11333,10 @@
         <v>8</v>
       </c>
       <c r="C697" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D697">
-        <v>-1.38045891394555</v>
+        <v>100.103033619565</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -11347,10 +11347,10 @@
         <v>8</v>
       </c>
       <c r="C698" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D698">
-        <v>1.71224507374451</v>
+        <v>99.97733235176079</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -11361,10 +11361,10 @@
         <v>8</v>
       </c>
       <c r="C699" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D699">
-        <v>2.55365332112282</v>
+        <v>99.491082642686</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -11375,10 +11375,10 @@
         <v>8</v>
       </c>
       <c r="C700" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D700">
-        <v>-3.58632952390045</v>
+        <v>99.49421925153131</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -11389,10 +11389,10 @@
         <v>8</v>
       </c>
       <c r="C701" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D701">
-        <v>-7.68997160240828</v>
+        <v>102.651940476089</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -11403,10 +11403,10 @@
         <v>8</v>
       </c>
       <c r="C702" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D702">
-        <v>-1.24095688179896</v>
+        <v>100.434298894287</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -11417,10 +11417,10 @@
         <v>8</v>
       </c>
       <c r="C703" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D703">
-        <v>-3.07736653146024</v>
+        <v>101.553253327191</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -11431,10 +11431,10 @@
         <v>8</v>
       </c>
       <c r="C704" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D704">
-        <v>-5.2132551316649</v>
+        <v>102.027159454144</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -11445,10 +11445,10 @@
         <v>8</v>
       </c>
       <c r="C705" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D705">
-        <v>-2.11762998157527</v>
+        <v>100.138750386422</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -11459,10 +11459,10 @@
         <v>8</v>
       </c>
       <c r="C706" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D706">
-        <v>-7.06578980671148</v>
+        <v>102.256217093888</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -11473,10 +11473,10 @@
         <v>8</v>
       </c>
       <c r="C707" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D707">
-        <v>-6.27590904496796</v>
+        <v>101.893346319552</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -11487,10 +11487,10 @@
         <v>8</v>
       </c>
       <c r="C708" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D708">
-        <v>-7.97678360616846</v>
+        <v>102.557256983332</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -11501,10 +11501,10 @@
         <v>8</v>
       </c>
       <c r="C709" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="D709">
-        <v>-3.81895169182063</v>
+        <v>98.7211523688338</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -11515,10 +11515,10 @@
         <v>8</v>
       </c>
       <c r="C710" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D710">
-        <v>-7.75303916003561</v>
+        <v>101.689189299815</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -11529,10 +11529,10 @@
         <v>8</v>
       </c>
       <c r="C711" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="D711">
-        <v>-7.78762412439388</v>
+        <v>102.031739978812</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -11543,10 +11543,10 @@
         <v>8</v>
       </c>
       <c r="C712" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D712">
-        <v>-1.57945149392044</v>
+        <v>95.92602869193939</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -11557,10 +11557,10 @@
         <v>8</v>
       </c>
       <c r="C713" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="D713">
-        <v>-2.11670353087483</v>
+        <v>94.7580354041567</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -11571,10 +11571,10 @@
         <v>8</v>
       </c>
       <c r="C714" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D714">
-        <v>-7.32939738812204</v>
+        <v>99.18795255047181</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -11585,10 +11585,10 @@
         <v>8</v>
       </c>
       <c r="C715" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D715">
-        <v>-9.07060299710805</v>
+        <v>98.428087497691</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -11599,10 +11599,10 @@
         <v>8</v>
       </c>
       <c r="C716" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D716">
-        <v>-10.2003981873626</v>
+        <v>96.7082233282089</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -11613,10 +11613,10 @@
         <v>8</v>
       </c>
       <c r="C717" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D717">
-        <v>-38.0222653242644</v>
+        <v>98.0181821850643</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -11627,10 +11627,10 @@
         <v>8</v>
       </c>
       <c r="C718" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D718">
-        <v>-37.0111313716927</v>
+        <v>95.0310077297393</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -11641,10 +11641,10 @@
         <v>8</v>
       </c>
       <c r="C719" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D719">
-        <v>-23.5506487163258</v>
+        <v>95.4986125816627</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -11655,10 +11655,10 @@
         <v>8</v>
       </c>
       <c r="C720" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D720">
-        <v>-20.661193196044</v>
+        <v>94.37648652134951</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -11669,10 +11669,10 @@
         <v>8</v>
       </c>
       <c r="C721" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D721">
-        <v>-18.3536052488343</v>
+        <v>94.9510392502594</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -11683,10 +11683,10 @@
         <v>8</v>
       </c>
       <c r="C722" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="D722">
-        <v>-14.9428081356978</v>
+        <v>93.8051866318776</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -11697,10 +11697,10 @@
         <v>8</v>
       </c>
       <c r="C723" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D723">
-        <v>-14.3350283687604</v>
+        <v>94.0858915816832</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -11711,10 +11711,10 @@
         <v>8</v>
       </c>
       <c r="C724" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D724">
-        <v>-9.369412221733571</v>
+        <v>94.41092359870601</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -11725,10 +11725,10 @@
         <v>8</v>
       </c>
       <c r="C725" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D725">
-        <v>-10.7177433952765</v>
+        <v>92.7522887229693</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -11739,10 +11739,10 @@
         <v>8</v>
       </c>
       <c r="C726" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D726">
-        <v>-8.976342732138701</v>
+        <v>91.9180733469058</v>
       </c>
     </row>
     <row r="727" spans="1:4">
@@ -11753,10 +11753,10 @@
         <v>8</v>
       </c>
       <c r="C727" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="D727">
-        <v>-4.16490387192081</v>
+        <v>89.5000664431293</v>
       </c>
     </row>
     <row r="728" spans="1:4">
@@ -11767,10 +11767,10 @@
         <v>8</v>
       </c>
       <c r="C728" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D728">
-        <v>0.768615512348785</v>
+        <v>86.8435994688077</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -11781,10 +11781,10 @@
         <v>8</v>
       </c>
       <c r="C729" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D729">
-        <v>43.9757036357971</v>
+        <v>60.7494488886383</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -11795,10 +11795,10 @@
         <v>8</v>
       </c>
       <c r="C730" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="D730">
-        <v>45.2163226583787</v>
+        <v>59.858956615042</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -11809,10 +11809,10 @@
         <v>8</v>
       </c>
       <c r="C731" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D731">
-        <v>15.2569366318644</v>
+        <v>73.0080698035904</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -11823,10 +11823,10 @@
         <v>8</v>
       </c>
       <c r="C732" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D732">
-        <v>16.3329795516711</v>
+        <v>74.8771783095351</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -11837,10 +11837,10 @@
         <v>8</v>
       </c>
       <c r="C733" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="D733">
-        <v>13.9402855599448</v>
+        <v>77.5241003266011</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -11851,10 +11851,10 @@
         <v>8</v>
       </c>
       <c r="C734" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="D734">
-        <v>10.0179265193194</v>
+        <v>79.7880575721429</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -11865,10 +11865,10 @@
         <v>8</v>
       </c>
       <c r="C735" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D735">
-        <v>9.038265240773359</v>
+        <v>80.5986523324478</v>
       </c>
     </row>
     <row r="736" spans="1:4">
@@ -11879,10 +11879,10 @@
         <v>8</v>
       </c>
       <c r="C736" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D736">
-        <v>3.56904599232161</v>
+        <v>85.5651749843973</v>
       </c>
     </row>
     <row r="737" spans="1:4">
@@ -11893,10 +11893,10 @@
         <v>8</v>
       </c>
       <c r="C737" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D737">
-        <v>7.12471644393579</v>
+        <v>82.81133642439551</v>
       </c>
     </row>
     <row r="738" spans="1:4">
@@ -11907,10 +11907,10 @@
         <v>8</v>
       </c>
       <c r="C738" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D738">
-        <v>9.27702774252479</v>
+        <v>83.6671920505089</v>
       </c>
     </row>
     <row r="739" spans="1:4">
@@ -11921,10 +11921,10 @@
         <v>8</v>
       </c>
       <c r="C739" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D739">
-        <v>6.41552514155563</v>
+        <v>85.7724747104677</v>
       </c>
     </row>
     <row r="740" spans="1:4">
@@ -11935,10 +11935,10 @@
         <v>8</v>
       </c>
       <c r="C740" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="D740">
-        <v>7.92219810889755</v>
+        <v>87.511092845807</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -11949,10 +11949,10 @@
         <v>8</v>
       </c>
       <c r="C741" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="D741">
-        <v>8.06875645201279</v>
+        <v>87.4644464922859</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -11963,10 +11963,10 @@
         <v>8</v>
       </c>
       <c r="C742" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="D742">
-        <v>7.66214206284039</v>
+        <v>86.9249755780383</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -11977,10 +11977,10 @@
         <v>8</v>
       </c>
       <c r="C743" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D743">
-        <v>10.5310062581064</v>
+        <v>84.14686474967149</v>
       </c>
     </row>
     <row r="744" spans="1:4">
@@ -11991,10 +11991,10 @@
         <v>8</v>
       </c>
       <c r="C744" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="D744">
-        <v>5.64813627058623</v>
+        <v>87.1068525316998</v>
       </c>
     </row>
     <row r="745" spans="1:4">
@@ -12005,10 +12005,10 @@
         <v>8</v>
       </c>
       <c r="C745" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D745">
-        <v>6.64013325023093</v>
+        <v>88.33118128990741</v>
       </c>
     </row>
     <row r="746" spans="1:4">
@@ -12019,10 +12019,10 @@
         <v>8</v>
       </c>
       <c r="C746" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D746">
-        <v>6.68214381252287</v>
+        <v>87.7811665509124</v>
       </c>
     </row>
     <row r="747" spans="1:4">
@@ -12033,10 +12033,10 @@
         <v>8</v>
       </c>
       <c r="C747" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D747">
-        <v>7.49858256288102</v>
+        <v>87.8833723107432</v>
       </c>
     </row>
     <row r="748" spans="1:4">
@@ -12047,10 +12047,10 @@
         <v>8</v>
       </c>
       <c r="C748" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D748">
-        <v>8.840586689535691</v>
+        <v>88.6190354330009</v>
       </c>
     </row>
     <row r="749" spans="1:4">
@@ -12061,10 +12061,10 @@
         <v>8</v>
       </c>
       <c r="C749" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D749">
-        <v>12.7135645668641</v>
+        <v>88.7114093280674</v>
       </c>
     </row>
     <row r="750" spans="1:4">
@@ -12075,10 +12075,10 @@
         <v>8</v>
       </c>
       <c r="C750" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D750">
-        <v>9.962072448191829</v>
+        <v>91.42902066842611</v>
       </c>
     </row>
     <row r="751" spans="1:4">
@@ -12089,10 +12089,10 @@
         <v>8</v>
       </c>
       <c r="C751" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="D751">
-        <v>11.9750658057278</v>
+        <v>91.2752293900522</v>
       </c>
     </row>
     <row r="752" spans="1:4">
@@ -12103,10 +12103,10 @@
         <v>8</v>
       </c>
       <c r="C752" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D752">
-        <v>8.620029401186089</v>
+        <v>94.4438949883131</v>
       </c>
     </row>
     <row r="753" spans="1:4">
@@ -12117,10 +12117,10 @@
         <v>8</v>
       </c>
       <c r="C753" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="D753">
-        <v>8.71710500687508</v>
+        <v>94.52173966184949</v>
       </c>
     </row>
     <row r="754" spans="1:4">
@@ -12131,10 +12131,10 @@
         <v>8</v>
       </c>
       <c r="C754" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="D754">
-        <v>13.2155911531029</v>
+        <v>93.58529069491691</v>
       </c>
     </row>
     <row r="755" spans="1:4">
@@ -12145,10 +12145,10 @@
         <v>8</v>
       </c>
       <c r="C755" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D755">
-        <v>16.5388925268658</v>
+        <v>93.0083763424597</v>
       </c>
     </row>
     <row r="756" spans="1:4">
@@ -12159,10 +12159,10 @@
         <v>8</v>
       </c>
       <c r="C756" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D756">
-        <v>15.5466098996942</v>
+        <v>92.02676626370879</v>
       </c>
     </row>
     <row r="757" spans="1:4">
@@ -12173,10 +12173,10 @@
         <v>8</v>
       </c>
       <c r="C757" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D757">
-        <v>14.8745646625607</v>
+        <v>94.19648942906031</v>
       </c>
     </row>
     <row r="758" spans="1:4">
@@ -12187,10 +12187,10 @@
         <v>8</v>
       </c>
       <c r="C758" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D758">
-        <v>18.7715104888796</v>
+        <v>93.64683034015459</v>
       </c>
     </row>
     <row r="759" spans="1:4">
@@ -12201,10 +12201,10 @@
         <v>8</v>
       </c>
       <c r="C759" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D759">
-        <v>19.7438993956608</v>
+        <v>94.4733795425084</v>
       </c>
     </row>
     <row r="760" spans="1:4">
@@ -12215,10 +12215,10 @@
         <v>8</v>
       </c>
       <c r="C760" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D760">
-        <v>14.2659511693432</v>
+        <v>96.4534780838857</v>
       </c>
     </row>
     <row r="761" spans="1:4">
@@ -12229,10 +12229,10 @@
         <v>8</v>
       </c>
       <c r="C761" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D761">
-        <v>11.6874847116243</v>
+        <v>99.9897916311664</v>
       </c>
     </row>
     <row r="762" spans="1:4">
@@ -12243,10 +12243,10 @@
         <v>8</v>
       </c>
       <c r="C762" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="D762">
-        <v>11.9133979142952</v>
+        <v>100.537245946087</v>
       </c>
     </row>
     <row r="763" spans="1:4">
@@ -12257,10 +12257,10 @@
         <v>8</v>
       </c>
       <c r="C763" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D763">
-        <v>9.944910852884609</v>
+        <v>102.20549817384</v>
       </c>
     </row>
     <row r="764" spans="1:4">
@@ -12271,10 +12271,10 @@
         <v>8</v>
       </c>
       <c r="C764" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D764">
-        <v>8.87433215094701</v>
+        <v>102.584986503931</v>
       </c>
     </row>
     <row r="765" spans="1:4">
@@ -12285,10 +12285,10 @@
         <v>8</v>
       </c>
       <c r="C765" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="D765">
-        <v>9.15093721698066</v>
+        <v>102.761298962498</v>
       </c>
     </row>
     <row r="766" spans="1:4">
@@ -12299,10 +12299,10 @@
         <v>8</v>
       </c>
       <c r="C766" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D766">
-        <v>5.46889860009982</v>
+        <v>105.9531400926</v>
       </c>
     </row>
     <row r="767" spans="1:4">
@@ -12313,10 +12313,10 @@
         <v>8</v>
       </c>
       <c r="C767" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="D767">
-        <v>2.41463481140446</v>
+        <v>108.390931746722</v>
       </c>
     </row>
     <row r="768" spans="1:4">
@@ -12327,10 +12327,10 @@
         <v>8</v>
       </c>
       <c r="C768" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D768">
-        <v>6.75344788150688</v>
+        <v>106.333808618031</v>
       </c>
     </row>
     <row r="769" spans="1:4">
@@ -12341,10 +12341,10 @@
         <v>8</v>
       </c>
       <c r="C769" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D769">
-        <v>3.93749841620623</v>
+        <v>108.207807159048</v>
       </c>
     </row>
     <row r="770" spans="1:4">
@@ -12355,10 +12355,10 @@
         <v>8</v>
       </c>
       <c r="C770" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D770">
-        <v>-0.223039517438667</v>
+        <v>111.22575491996</v>
       </c>
     </row>
     <row r="771" spans="1:4">
@@ -12369,10 +12369,10 @@
         <v>8</v>
       </c>
       <c r="C771" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D771">
-        <v>-3.37115359212571</v>
+        <v>113.126108555062</v>
       </c>
     </row>
     <row r="772" spans="1:4">
@@ -12383,10 +12383,10 @@
         <v>8</v>
       </c>
       <c r="C772" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D772">
-        <v>-0.37145268142619</v>
+        <v>110.213484168466</v>
       </c>
     </row>
     <row r="773" spans="1:4">
@@ -12397,10 +12397,10 @@
         <v>8</v>
       </c>
       <c r="C773" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D773">
-        <v>-5.00302374505068</v>
+        <v>111.676083241244</v>
       </c>
     </row>
     <row r="774" spans="1:4">
@@ -12411,10 +12411,10 @@
         <v>8</v>
       </c>
       <c r="C774" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="D774">
-        <v>-6.50470362649427</v>
+        <v>112.514648107718</v>
       </c>
     </row>
     <row r="775" spans="1:4">
@@ -12425,10 +12425,10 @@
         <v>8</v>
       </c>
       <c r="C775" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="D775">
-        <v>-5.71784479359362</v>
+        <v>112.369743853975</v>
       </c>
     </row>
     <row r="776" spans="1:4">
@@ -12439,10 +12439,10 @@
         <v>8</v>
       </c>
       <c r="C776" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D776">
-        <v>-5.01248741828562</v>
+        <v>111.688718943294</v>
       </c>
     </row>
     <row r="777" spans="1:4">
@@ -12453,10 +12453,10 @@
         <v>8</v>
       </c>
       <c r="C777" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D777">
-        <v>-8.893096739250639</v>
+        <v>112.16492091391</v>
       </c>
     </row>
     <row r="778" spans="1:4">
@@ -12467,10 +12467,10 @@
         <v>8</v>
       </c>
       <c r="C778" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D778">
-        <v>-6.43732457823048</v>
+        <v>111.747609887886</v>
       </c>
     </row>
     <row r="779" spans="1:4">
@@ -12481,10 +12481,10 @@
         <v>8</v>
       </c>
       <c r="C779" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="D779">
-        <v>-7.23764711646527</v>
+        <v>111.008176917084</v>
       </c>
     </row>
     <row r="780" spans="1:4">
@@ -12495,10 +12495,10 @@
         <v>8</v>
       </c>
       <c r="C780" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="D780">
-        <v>-7.64125666842735</v>
+        <v>113.515006963471</v>
       </c>
     </row>
     <row r="781" spans="1:4">
@@ -12509,10 +12509,10 @@
         <v>8</v>
       </c>
       <c r="C781" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D781">
-        <v>-9.37244406623787</v>
+        <v>112.468487852147</v>
       </c>
     </row>
     <row r="782" spans="1:4">
@@ -12523,10 +12523,10 @@
         <v>8</v>
       </c>
       <c r="C782" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="D782">
-        <v>-8.0606265228199</v>
+        <v>110.977677532919</v>
       </c>
     </row>
     <row r="783" spans="1:4">
@@ -12537,10 +12537,10 @@
         <v>8</v>
       </c>
       <c r="C783" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="D783">
-        <v>-5.7480874273727</v>
+        <v>109.312453682876</v>
       </c>
     </row>
     <row r="784" spans="1:4">
@@ -12551,10 +12551,10 @@
         <v>8</v>
       </c>
       <c r="C784" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="D784">
-        <v>-5.64312010618823</v>
+        <v>109.804093226229</v>
       </c>
     </row>
     <row r="785" spans="1:4">
@@ -12565,10 +12565,10 @@
         <v>8</v>
       </c>
       <c r="C785" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="D785">
-        <v>-1.91517498704337</v>
+        <v>106.088902279142</v>
       </c>
     </row>
     <row r="786" spans="1:4">
@@ -12579,10 +12579,10 @@
         <v>8</v>
       </c>
       <c r="C786" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="D786">
-        <v>-2.06436777781394</v>
+        <v>105.195903711918</v>
       </c>
     </row>
     <row r="787" spans="1:4">
@@ -12593,10 +12593,10 @@
         <v>8</v>
       </c>
       <c r="C787" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="D787">
-        <v>-3.10498962167925</v>
+        <v>105.944616305446</v>
       </c>
     </row>
     <row r="788" spans="1:4">
@@ -12607,10 +12607,10 @@
         <v>8</v>
       </c>
       <c r="C788" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="D788">
-        <v>-2.67188624429723</v>
+        <v>106.090335958617</v>
       </c>
     </row>
     <row r="789" spans="1:4">
@@ -12621,10 +12621,10 @@
         <v>8</v>
       </c>
       <c r="C789" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="D789">
-        <v>5.21303666445429</v>
+        <v>102.189985989532</v>
       </c>
     </row>
     <row r="790" spans="1:4">
@@ -12635,178 +12635,178 @@
         <v>8</v>
       </c>
       <c r="C790" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="D790">
-        <v>2.41673801889479</v>
+        <v>104.554053530988</v>
       </c>
     </row>
     <row r="791" spans="1:4">
       <c r="A791" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B791" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C791" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="D791">
-        <v>54.5551565641348</v>
+        <v>102.973796801404</v>
       </c>
     </row>
     <row r="792" spans="1:4">
       <c r="A792" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B792" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C792" t="s">
-        <v>10</v>
+        <v>399</v>
       </c>
       <c r="D792">
-        <v>55.7277000024058</v>
+        <v>104.841033924209</v>
       </c>
     </row>
     <row r="793" spans="1:4">
       <c r="A793" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B793" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C793" t="s">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="D793">
-        <v>56.4972565915955</v>
+        <v>101.927441736061</v>
       </c>
     </row>
     <row r="794" spans="1:4">
       <c r="A794" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B794" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C794" t="s">
-        <v>12</v>
+        <v>401</v>
       </c>
       <c r="D794">
-        <v>56.000165103122</v>
+        <v>102.032181423291</v>
       </c>
     </row>
     <row r="795" spans="1:4">
       <c r="A795" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B795" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C795" t="s">
-        <v>13</v>
+        <v>402</v>
       </c>
       <c r="D795">
-        <v>57.0623529372104</v>
+        <v>103.029078276178</v>
       </c>
     </row>
     <row r="796" spans="1:4">
       <c r="A796" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B796" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C796" t="s">
-        <v>14</v>
+        <v>403</v>
       </c>
       <c r="D796">
-        <v>54.9042665777449</v>
+        <v>103.607716363962</v>
       </c>
     </row>
     <row r="797" spans="1:4">
       <c r="A797" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B797" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C797" t="s">
-        <v>15</v>
+        <v>404</v>
       </c>
       <c r="D797">
-        <v>55.8380860676937</v>
+        <v>104.057114158663</v>
       </c>
     </row>
     <row r="798" spans="1:4">
       <c r="A798" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B798" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C798" t="s">
-        <v>16</v>
+        <v>405</v>
       </c>
       <c r="D798">
-        <v>57.3125001378712</v>
+        <v>103.024273372109</v>
       </c>
     </row>
     <row r="799" spans="1:4">
       <c r="A799" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B799" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C799" t="s">
-        <v>17</v>
+        <v>406</v>
       </c>
       <c r="D799">
-        <v>57.9233959877892</v>
+        <v>102.655046964434</v>
       </c>
     </row>
     <row r="800" spans="1:4">
       <c r="A800" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B800" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C800" t="s">
-        <v>18</v>
+        <v>407</v>
       </c>
       <c r="D800">
-        <v>59.2054917407515</v>
+        <v>103.25572286561</v>
       </c>
     </row>
     <row r="801" spans="1:4">
       <c r="A801" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B801" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C801" t="s">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="D801">
-        <v>61.3075447264138</v>
+        <v>107.517187426567</v>
       </c>
     </row>
     <row r="802" spans="1:4">
       <c r="A802" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B802" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C802" t="s">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="D802">
-        <v>60.961176270989</v>
+        <v>107.080851092967</v>
       </c>
     </row>
     <row r="803" spans="1:4">
@@ -12820,7 +12820,7 @@
         <v>21</v>
       </c>
       <c r="D803">
-        <v>62.386817683124</v>
+        <v>14.3554919685408</v>
       </c>
     </row>
     <row r="804" spans="1:4">
@@ -12834,7 +12834,7 @@
         <v>22</v>
       </c>
       <c r="D804">
-        <v>63.9611875394791</v>
+        <v>14.7744973087313</v>
       </c>
     </row>
     <row r="805" spans="1:4">
@@ -12848,7 +12848,7 @@
         <v>23</v>
       </c>
       <c r="D805">
-        <v>65.9645919247083</v>
+        <v>16.7571593812949</v>
       </c>
     </row>
     <row r="806" spans="1:4">
@@ -12862,7 +12862,7 @@
         <v>24</v>
       </c>
       <c r="D806">
-        <v>67.5760919972119</v>
+        <v>20.6712370807717</v>
       </c>
     </row>
     <row r="807" spans="1:4">
@@ -12876,7 +12876,7 @@
         <v>25</v>
       </c>
       <c r="D807">
-        <v>66.036145049922</v>
+        <v>15.7262917682103</v>
       </c>
     </row>
     <row r="808" spans="1:4">
@@ -12890,7 +12890,7 @@
         <v>26</v>
       </c>
       <c r="D808">
-        <v>66.2846249354706</v>
+        <v>20.7276393385768</v>
       </c>
     </row>
     <row r="809" spans="1:4">
@@ -12904,7 +12904,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>66.1280731924943</v>
+        <v>18.4282590064527</v>
       </c>
     </row>
     <row r="810" spans="1:4">
@@ -12918,7 +12918,7 @@
         <v>28</v>
       </c>
       <c r="D810">
-        <v>66.5851138712836</v>
+        <v>16.1790424621263</v>
       </c>
     </row>
     <row r="811" spans="1:4">
@@ -12932,7 +12932,7 @@
         <v>29</v>
       </c>
       <c r="D811">
-        <v>65.67043143318089</v>
+        <v>13.3746223150052</v>
       </c>
     </row>
     <row r="812" spans="1:4">
@@ -12946,7 +12946,7 @@
         <v>30</v>
       </c>
       <c r="D812">
-        <v>66.5739032961158</v>
+        <v>12.4454866241616</v>
       </c>
     </row>
     <row r="813" spans="1:4">
@@ -12960,7 +12960,7 @@
         <v>31</v>
       </c>
       <c r="D813">
-        <v>65.24421299075981</v>
+        <v>6.42118075664825</v>
       </c>
     </row>
     <row r="814" spans="1:4">
@@ -12974,7 +12974,7 @@
         <v>32</v>
       </c>
       <c r="D814">
-        <v>58.160696435453</v>
+        <v>-4.59387434239639</v>
       </c>
     </row>
     <row r="815" spans="1:4">
@@ -12988,7 +12988,7 @@
         <v>33</v>
       </c>
       <c r="D815">
-        <v>51.2702905860598</v>
+        <v>-17.8187115642401</v>
       </c>
     </row>
     <row r="816" spans="1:4">
@@ -13002,7 +13002,7 @@
         <v>34</v>
       </c>
       <c r="D816">
-        <v>42.3394399024385</v>
+        <v>-33.8044812312074</v>
       </c>
     </row>
     <row r="817" spans="1:4">
@@ -13016,7 +13016,7 @@
         <v>35</v>
       </c>
       <c r="D817">
-        <v>42.3730917279644</v>
+        <v>-35.7638840905302</v>
       </c>
     </row>
     <row r="818" spans="1:4">
@@ -13030,7 +13030,7 @@
         <v>36</v>
       </c>
       <c r="D818">
-        <v>41.5102626099472</v>
+        <v>-38.5725611187166</v>
       </c>
     </row>
     <row r="819" spans="1:4">
@@ -13044,7 +13044,7 @@
         <v>37</v>
       </c>
       <c r="D819">
-        <v>38.4227660505211</v>
+        <v>-41.8155526470022</v>
       </c>
     </row>
     <row r="820" spans="1:4">
@@ -13058,7 +13058,7 @@
         <v>38</v>
       </c>
       <c r="D820">
-        <v>40.1371693905036</v>
+        <v>-39.4472406993659</v>
       </c>
     </row>
     <row r="821" spans="1:4">
@@ -13072,7 +13072,7 @@
         <v>39</v>
       </c>
       <c r="D821">
-        <v>40.3414560554434</v>
+        <v>-38.994962187977</v>
       </c>
     </row>
     <row r="822" spans="1:4">
@@ -13086,7 +13086,7 @@
         <v>40</v>
       </c>
       <c r="D822">
-        <v>40.7379875641879</v>
+        <v>-38.8181754214028</v>
       </c>
     </row>
     <row r="823" spans="1:4">
@@ -13100,7 +13100,7 @@
         <v>41</v>
       </c>
       <c r="D823">
-        <v>42.7470414634539</v>
+        <v>-34.9067144366965</v>
       </c>
     </row>
     <row r="824" spans="1:4">
@@ -13114,7 +13114,7 @@
         <v>42</v>
       </c>
       <c r="D824">
-        <v>42.892408068368</v>
+        <v>-35.5717391579314</v>
       </c>
     </row>
     <row r="825" spans="1:4">
@@ -13128,7 +13128,7 @@
         <v>43</v>
       </c>
       <c r="D825">
-        <v>44.490047498212</v>
+        <v>-31.8099714000491</v>
       </c>
     </row>
     <row r="826" spans="1:4">
@@ -13142,7 +13142,7 @@
         <v>44</v>
       </c>
       <c r="D826">
-        <v>46.2127224794326</v>
+        <v>-20.5430379763081</v>
       </c>
     </row>
     <row r="827" spans="1:4">
@@ -13156,7 +13156,7 @@
         <v>45</v>
       </c>
       <c r="D827">
-        <v>47.0583411468555</v>
+        <v>-8.21518542426502</v>
       </c>
     </row>
     <row r="828" spans="1:4">
@@ -13170,7 +13170,7 @@
         <v>46</v>
       </c>
       <c r="D828">
-        <v>45.7715380463156</v>
+        <v>8.10614914081428</v>
       </c>
     </row>
     <row r="829" spans="1:4">
@@ -13184,7 +13184,7 @@
         <v>47</v>
       </c>
       <c r="D829">
-        <v>46.352371350557</v>
+        <v>9.391053284805389</v>
       </c>
     </row>
     <row r="830" spans="1:4">
@@ -13198,7 +13198,7 @@
         <v>48</v>
       </c>
       <c r="D830">
-        <v>48.1707354108878</v>
+        <v>16.0453641633781</v>
       </c>
     </row>
     <row r="831" spans="1:4">
@@ -13212,7 +13212,7 @@
         <v>49</v>
       </c>
       <c r="D831">
-        <v>49.0452162307121</v>
+        <v>27.646240164552</v>
       </c>
     </row>
     <row r="832" spans="1:4">
@@ -13226,7 +13226,7 @@
         <v>50</v>
       </c>
       <c r="D832">
-        <v>50.7667430896991</v>
+        <v>26.4831174211065</v>
       </c>
     </row>
     <row r="833" spans="1:4">
@@ -13240,7 +13240,7 @@
         <v>51</v>
       </c>
       <c r="D833">
-        <v>52.1009605679807</v>
+        <v>29.1499258142185</v>
       </c>
     </row>
     <row r="834" spans="1:4">
@@ -13254,7 +13254,7 @@
         <v>52</v>
       </c>
       <c r="D834">
-        <v>52.1016845316498</v>
+        <v>27.8945957984718</v>
       </c>
     </row>
     <row r="835" spans="1:4">
@@ -13268,7 +13268,7 @@
         <v>53</v>
       </c>
       <c r="D835">
-        <v>52.6149791079368</v>
+        <v>23.0844926494372</v>
       </c>
     </row>
     <row r="836" spans="1:4">
@@ -13282,7 +13282,7 @@
         <v>54</v>
       </c>
       <c r="D836">
-        <v>54.1915312488027</v>
+        <v>26.3429443327699</v>
       </c>
     </row>
     <row r="837" spans="1:4">
@@ -13296,7 +13296,7 @@
         <v>55</v>
       </c>
       <c r="D837">
-        <v>53.8912000867808</v>
+        <v>21.1309115571221</v>
       </c>
     </row>
     <row r="838" spans="1:4">
@@ -13310,7 +13310,7 @@
         <v>56</v>
       </c>
       <c r="D838">
-        <v>55.3627462207145</v>
+        <v>19.7997937588598</v>
       </c>
     </row>
     <row r="839" spans="1:4">
@@ -13324,7 +13324,7 @@
         <v>57</v>
       </c>
       <c r="D839">
-        <v>53.6226571918154</v>
+        <v>13.9493145847929</v>
       </c>
     </row>
     <row r="840" spans="1:4">
@@ -13338,7 +13338,7 @@
         <v>58</v>
       </c>
       <c r="D840">
-        <v>54.2916084669882</v>
+        <v>18.6143415413554</v>
       </c>
     </row>
     <row r="841" spans="1:4">
@@ -13352,7 +13352,7 @@
         <v>59</v>
       </c>
       <c r="D841">
-        <v>54.4184824497701</v>
+        <v>17.4017226394096</v>
       </c>
     </row>
     <row r="842" spans="1:4">
@@ -13366,7 +13366,7 @@
         <v>60</v>
       </c>
       <c r="D842">
-        <v>57.1246695746754</v>
+        <v>18.5879125311502</v>
       </c>
     </row>
     <row r="843" spans="1:4">
@@ -13380,7 +13380,7 @@
         <v>61</v>
       </c>
       <c r="D843">
-        <v>58.1323313873877</v>
+        <v>18.5280356680031</v>
       </c>
     </row>
     <row r="844" spans="1:4">
@@ -13394,7 +13394,7 @@
         <v>62</v>
       </c>
       <c r="D844">
-        <v>59.1193064710709</v>
+        <v>16.4528249657729</v>
       </c>
     </row>
     <row r="845" spans="1:4">
@@ -13408,7 +13408,7 @@
         <v>63</v>
       </c>
       <c r="D845">
-        <v>59.3434143788944</v>
+        <v>13.9008066875539</v>
       </c>
     </row>
     <row r="846" spans="1:4">
@@ -13422,7 +13422,7 @@
         <v>64</v>
       </c>
       <c r="D846">
-        <v>60.9930795561012</v>
+        <v>17.0654655494876</v>
       </c>
     </row>
     <row r="847" spans="1:4">
@@ -13436,7 +13436,7 @@
         <v>65</v>
       </c>
       <c r="D847">
-        <v>60.5199138653809</v>
+        <v>15.0241145990528</v>
       </c>
     </row>
     <row r="848" spans="1:4">
@@ -13450,7 +13450,7 @@
         <v>66</v>
       </c>
       <c r="D848">
-        <v>60.7788016558143</v>
+        <v>12.1555347398624</v>
       </c>
     </row>
     <row r="849" spans="1:4">
@@ -13464,7 +13464,7 @@
         <v>67</v>
       </c>
       <c r="D849">
-        <v>62.7696944292645</v>
+        <v>16.4748499350296</v>
       </c>
     </row>
     <row r="850" spans="1:4">
@@ -13478,7 +13478,7 @@
         <v>68</v>
       </c>
       <c r="D850">
-        <v>60.9550247214041</v>
+        <v>10.1011580574325</v>
       </c>
     </row>
     <row r="851" spans="1:4">
@@ -13492,7 +13492,7 @@
         <v>69</v>
       </c>
       <c r="D851">
-        <v>60.8238600943953</v>
+        <v>13.4294033151327</v>
       </c>
     </row>
     <row r="852" spans="1:4">
@@ -13506,7 +13506,7 @@
         <v>70</v>
       </c>
       <c r="D852">
-        <v>65.224446719658</v>
+        <v>20.1372524435659</v>
       </c>
     </row>
     <row r="853" spans="1:4">
@@ -13520,7 +13520,7 @@
         <v>71</v>
       </c>
       <c r="D853">
-        <v>66.1996253851695</v>
+        <v>21.6491574278532</v>
       </c>
     </row>
     <row r="854" spans="1:4">
@@ -13534,7 +13534,7 @@
         <v>72</v>
       </c>
       <c r="D854">
-        <v>64.3684913933206</v>
+        <v>12.6807242345198</v>
       </c>
     </row>
     <row r="855" spans="1:4">
@@ -13548,7 +13548,7 @@
         <v>73</v>
       </c>
       <c r="D855">
-        <v>66.85554915162879</v>
+        <v>15.0057937743981</v>
       </c>
     </row>
     <row r="856" spans="1:4">
@@ -13562,7 +13562,7 @@
         <v>74</v>
       </c>
       <c r="D856">
-        <v>64.2023629173183</v>
+        <v>8.59796359203691</v>
       </c>
     </row>
     <row r="857" spans="1:4">
@@ -13576,7 +13576,7 @@
         <v>75</v>
       </c>
       <c r="D857">
-        <v>65.1954864419572</v>
+        <v>9.86136730471663</v>
       </c>
     </row>
     <row r="858" spans="1:4">
@@ -13590,7 +13590,7 @@
         <v>76</v>
       </c>
       <c r="D858">
-        <v>64.83356602013851</v>
+        <v>6.29659379717799</v>
       </c>
     </row>
     <row r="859" spans="1:4">
@@ -13604,7 +13604,7 @@
         <v>77</v>
       </c>
       <c r="D859">
-        <v>66.29401415342051</v>
+        <v>9.54082700924423</v>
       </c>
     </row>
     <row r="860" spans="1:4">
@@ -13618,7 +13618,7 @@
         <v>78</v>
       </c>
       <c r="D860">
-        <v>65.5460739673827</v>
+        <v>7.84364314809149</v>
       </c>
     </row>
     <row r="861" spans="1:4">
@@ -13632,7 +13632,7 @@
         <v>79</v>
       </c>
       <c r="D861">
-        <v>64.2331479603413</v>
+        <v>2.33146511924791</v>
       </c>
     </row>
     <row r="862" spans="1:4">
@@ -13646,7 +13646,7 @@
         <v>80</v>
       </c>
       <c r="D862">
-        <v>65.1966982034178</v>
+        <v>6.95869372771208</v>
       </c>
     </row>
     <row r="863" spans="1:4">
@@ -13660,7 +13660,7 @@
         <v>81</v>
       </c>
       <c r="D863">
-        <v>67.2396440559769</v>
+        <v>10.5481367864924</v>
       </c>
     </row>
     <row r="864" spans="1:4">
@@ -13674,7 +13674,7 @@
         <v>82</v>
       </c>
       <c r="D864">
-        <v>67.4653564581975</v>
+        <v>3.43568991573234</v>
       </c>
     </row>
     <row r="865" spans="1:4">
@@ -13688,7 +13688,7 @@
         <v>83</v>
       </c>
       <c r="D865">
-        <v>68.317134896254</v>
+        <v>3.19867295134103</v>
       </c>
     </row>
     <row r="866" spans="1:4">
@@ -13702,7 +13702,7 @@
         <v>84</v>
       </c>
       <c r="D866">
-        <v>67.5198370875212</v>
+        <v>4.89578926892111</v>
       </c>
     </row>
     <row r="867" spans="1:4">
@@ -13716,7 +13716,7 @@
         <v>85</v>
       </c>
       <c r="D867">
-        <v>67.37013679369259</v>
+        <v>0.769700718330372</v>
       </c>
     </row>
     <row r="868" spans="1:4">
@@ -13730,7 +13730,7 @@
         <v>86</v>
       </c>
       <c r="D868">
-        <v>68.0295530621275</v>
+        <v>5.96113596276507</v>
       </c>
     </row>
     <row r="869" spans="1:4">
@@ -13744,7 +13744,7 @@
         <v>87</v>
       </c>
       <c r="D869">
-        <v>66.5299057205545</v>
+        <v>2.04679702756005</v>
       </c>
     </row>
     <row r="870" spans="1:4">
@@ -13758,7 +13758,7 @@
         <v>88</v>
       </c>
       <c r="D870">
-        <v>67.3538517150574</v>
+        <v>3.88731616912149</v>
       </c>
     </row>
     <row r="871" spans="1:4">
@@ -13772,7 +13772,7 @@
         <v>89</v>
       </c>
       <c r="D871">
-        <v>67.1396393637974</v>
+        <v>1.27556796971128</v>
       </c>
     </row>
     <row r="872" spans="1:4">
@@ -13786,7 +13786,7 @@
         <v>90</v>
       </c>
       <c r="D872">
-        <v>67.76357544429359</v>
+        <v>3.38311868688639</v>
       </c>
     </row>
     <row r="873" spans="1:4">
@@ -13800,7 +13800,7 @@
         <v>91</v>
       </c>
       <c r="D873">
-        <v>68.5309849315172</v>
+        <v>6.69099539357694</v>
       </c>
     </row>
     <row r="874" spans="1:4">
@@ -13814,7 +13814,7 @@
         <v>92</v>
       </c>
       <c r="D874">
-        <v>70.00039345769559</v>
+        <v>7.36800388156156</v>
       </c>
     </row>
     <row r="875" spans="1:4">
@@ -13828,7 +13828,7 @@
         <v>93</v>
       </c>
       <c r="D875">
-        <v>70.5396845574184</v>
+        <v>4.9078791950389</v>
       </c>
     </row>
     <row r="876" spans="1:4">
@@ -13842,7 +13842,7 @@
         <v>94</v>
       </c>
       <c r="D876">
-        <v>70.752699801611</v>
+        <v>4.87263910841467</v>
       </c>
     </row>
     <row r="877" spans="1:4">
@@ -13856,7 +13856,7 @@
         <v>95</v>
       </c>
       <c r="D877">
-        <v>70.0897239043553</v>
+        <v>2.59464775680821</v>
       </c>
     </row>
     <row r="878" spans="1:4">
@@ -13870,7 +13870,7 @@
         <v>96</v>
       </c>
       <c r="D878">
-        <v>72.21255122724099</v>
+        <v>6.95012657337571</v>
       </c>
     </row>
     <row r="879" spans="1:4">
@@ -13884,7 +13884,7 @@
         <v>97</v>
       </c>
       <c r="D879">
-        <v>71.73063834395229</v>
+        <v>6.4724546479887</v>
       </c>
     </row>
     <row r="880" spans="1:4">
@@ -13898,7 +13898,7 @@
         <v>98</v>
       </c>
       <c r="D880">
-        <v>71.7653971400235</v>
+        <v>5.49150172202992</v>
       </c>
     </row>
     <row r="881" spans="1:4">
@@ -13912,7 +13912,7 @@
         <v>99</v>
       </c>
       <c r="D881">
-        <v>71.9708185051023</v>
+        <v>8.17814594146769</v>
       </c>
     </row>
     <row r="882" spans="1:4">
@@ -13926,7 +13926,7 @@
         <v>100</v>
       </c>
       <c r="D882">
-        <v>72.2415106936387</v>
+        <v>7.25668815386935</v>
       </c>
     </row>
     <row r="883" spans="1:4">
@@ -13940,7 +13940,7 @@
         <v>101</v>
       </c>
       <c r="D883">
-        <v>70.9736642757086</v>
+        <v>5.71052354204118</v>
       </c>
     </row>
     <row r="884" spans="1:4">
@@ -13954,7 +13954,7 @@
         <v>102</v>
       </c>
       <c r="D884">
-        <v>71.83359877227529</v>
+        <v>6.00621100834259</v>
       </c>
     </row>
     <row r="885" spans="1:4">
@@ -13968,7 +13968,7 @@
         <v>103</v>
       </c>
       <c r="D885">
-        <v>70.6006082693401</v>
+        <v>3.01998189562148</v>
       </c>
     </row>
     <row r="886" spans="1:4">
@@ -13982,7 +13982,7 @@
         <v>104</v>
       </c>
       <c r="D886">
-        <v>68.5137613388147</v>
+        <v>-2.12374823261434</v>
       </c>
     </row>
     <row r="887" spans="1:4">
@@ -13996,7 +13996,7 @@
         <v>105</v>
       </c>
       <c r="D887">
-        <v>67.7705530858867</v>
+        <v>-3.92563631224868</v>
       </c>
     </row>
     <row r="888" spans="1:4">
@@ -14010,7 +14010,7 @@
         <v>106</v>
       </c>
       <c r="D888">
-        <v>67.11320366664209</v>
+        <v>-5.14396785588956</v>
       </c>
     </row>
     <row r="889" spans="1:4">
@@ -14024,7 +14024,7 @@
         <v>107</v>
       </c>
       <c r="D889">
-        <v>66.8979604296826</v>
+        <v>-4.55382514992952</v>
       </c>
     </row>
     <row r="890" spans="1:4">
@@ -14038,7 +14038,7 @@
         <v>108</v>
       </c>
       <c r="D890">
-        <v>65.5534274577976</v>
+        <v>-9.221560042226219</v>
       </c>
     </row>
     <row r="891" spans="1:4">
@@ -14052,7 +14052,7 @@
         <v>109</v>
       </c>
       <c r="D891">
-        <v>65.0890758977561</v>
+        <v>-9.25903156521421</v>
       </c>
     </row>
     <row r="892" spans="1:4">
@@ -14066,7 +14066,7 @@
         <v>110</v>
       </c>
       <c r="D892">
-        <v>65.5588362106125</v>
+        <v>-8.64840323714952</v>
       </c>
     </row>
     <row r="893" spans="1:4">
@@ -14080,7 +14080,7 @@
         <v>111</v>
       </c>
       <c r="D893">
-        <v>67.0659283208774</v>
+        <v>-6.81510963207563</v>
       </c>
     </row>
     <row r="894" spans="1:4">
@@ -14094,7 +14094,7 @@
         <v>112</v>
       </c>
       <c r="D894">
-        <v>66.662543758453</v>
+        <v>-7.72266094883446</v>
       </c>
     </row>
     <row r="895" spans="1:4">
@@ -14108,7 +14108,7 @@
         <v>113</v>
       </c>
       <c r="D895">
-        <v>66.8089341927185</v>
+        <v>-5.86799360789876</v>
       </c>
     </row>
     <row r="896" spans="1:4">
@@ -14122,7 +14122,7 @@
         <v>114</v>
       </c>
       <c r="D896">
-        <v>64.8622778455006</v>
+        <v>-9.704819257176529</v>
       </c>
     </row>
     <row r="897" spans="1:4">
@@ -14136,7 +14136,7 @@
         <v>115</v>
       </c>
       <c r="D897">
-        <v>65.8946466065144</v>
+        <v>-6.66561064866826</v>
       </c>
     </row>
     <row r="898" spans="1:4">
@@ -14150,7 +14150,7 @@
         <v>116</v>
       </c>
       <c r="D898">
-        <v>66.3039783043634</v>
+        <v>-3.22531268356947</v>
       </c>
     </row>
     <row r="899" spans="1:4">
@@ -14164,7 +14164,7 @@
         <v>117</v>
       </c>
       <c r="D899">
-        <v>64.51919777610981</v>
+        <v>-4.79759299832835</v>
       </c>
     </row>
     <row r="900" spans="1:4">
@@ -14178,7 +14178,7 @@
         <v>118</v>
       </c>
       <c r="D900">
-        <v>63.9998066926348</v>
+        <v>-4.63902302961403</v>
       </c>
     </row>
     <row r="901" spans="1:4">
@@ -14192,7 +14192,7 @@
         <v>119</v>
       </c>
       <c r="D901">
-        <v>62.3759485850665</v>
+        <v>-6.75956608478258</v>
       </c>
     </row>
     <row r="902" spans="1:4">
@@ -14206,7 +14206,7 @@
         <v>120</v>
       </c>
       <c r="D902">
-        <v>63.5895200152001</v>
+        <v>-2.99588826817916</v>
       </c>
     </row>
     <row r="903" spans="1:4">
@@ -14220,7 +14220,7 @@
         <v>121</v>
       </c>
       <c r="D903">
-        <v>64.6159009437725</v>
+        <v>-0.7269652356516469</v>
       </c>
     </row>
     <row r="904" spans="1:4">
@@ -14234,7 +14234,7 @@
         <v>122</v>
       </c>
       <c r="D904">
-        <v>64.01809820664261</v>
+        <v>-2.35016069995532</v>
       </c>
     </row>
     <row r="905" spans="1:4">
@@ -14248,7 +14248,7 @@
         <v>123</v>
       </c>
       <c r="D905">
-        <v>64.8427615435959</v>
+        <v>-3.31489749406696</v>
       </c>
     </row>
     <row r="906" spans="1:4">
@@ -14262,7 +14262,7 @@
         <v>124</v>
       </c>
       <c r="D906">
-        <v>65.0093420560804</v>
+        <v>-2.47995592301857</v>
       </c>
     </row>
     <row r="907" spans="1:4">
@@ -14276,7 +14276,7 @@
         <v>125</v>
       </c>
       <c r="D907">
-        <v>66.3103429134718</v>
+        <v>-0.746294317176875</v>
       </c>
     </row>
     <row r="908" spans="1:4">
@@ -14290,7 +14290,7 @@
         <v>126</v>
       </c>
       <c r="D908">
-        <v>65.94173781407549</v>
+        <v>1.66423382654881</v>
       </c>
     </row>
     <row r="909" spans="1:4">
@@ -14304,7 +14304,7 @@
         <v>127</v>
       </c>
       <c r="D909">
-        <v>66.78410168316</v>
+        <v>1.34981386569523</v>
       </c>
     </row>
     <row r="910" spans="1:4">
@@ -14318,7 +14318,7 @@
         <v>128</v>
       </c>
       <c r="D910">
-        <v>65.9636720813817</v>
+        <v>-0.513251590152774</v>
       </c>
     </row>
     <row r="911" spans="1:4">
@@ -14332,7 +14332,7 @@
         <v>129</v>
       </c>
       <c r="D911">
-        <v>65.9403950986717</v>
+        <v>2.20275107494926</v>
       </c>
     </row>
     <row r="912" spans="1:4">
@@ -14346,7 +14346,7 @@
         <v>130</v>
       </c>
       <c r="D912">
-        <v>67.437152005336</v>
+        <v>5.3708682734143</v>
       </c>
     </row>
     <row r="913" spans="1:4">
@@ -14360,7 +14360,7 @@
         <v>131</v>
       </c>
       <c r="D913">
-        <v>66.1013933105978</v>
+        <v>5.97256604514903</v>
       </c>
     </row>
     <row r="914" spans="1:4">
@@ -14374,7 +14374,7 @@
         <v>132</v>
       </c>
       <c r="D914">
-        <v>66.83016074033679</v>
+        <v>5.09618679990361</v>
       </c>
     </row>
     <row r="915" spans="1:4">
@@ -14388,7 +14388,7 @@
         <v>133</v>
       </c>
       <c r="D915">
-        <v>65.87819193705759</v>
+        <v>1.95352997458553</v>
       </c>
     </row>
     <row r="916" spans="1:4">
@@ -14402,7 +14402,7 @@
         <v>134</v>
       </c>
       <c r="D916">
-        <v>66.5410691839525</v>
+        <v>3.94102769058533</v>
       </c>
     </row>
     <row r="917" spans="1:4">
@@ -14416,7 +14416,7 @@
         <v>135</v>
       </c>
       <c r="D917">
-        <v>66.3908294946265</v>
+        <v>2.38741829338929</v>
       </c>
     </row>
     <row r="918" spans="1:4">
@@ -14430,7 +14430,7 @@
         <v>136</v>
       </c>
       <c r="D918">
-        <v>66.41095126601741</v>
+        <v>2.15601199090418</v>
       </c>
     </row>
     <row r="919" spans="1:4">
@@ -14444,7 +14444,7 @@
         <v>137</v>
       </c>
       <c r="D919">
-        <v>64.8815561035715</v>
+        <v>-2.15469675939502</v>
       </c>
     </row>
     <row r="920" spans="1:4">
@@ -14458,7 +14458,7 @@
         <v>138</v>
       </c>
       <c r="D920">
-        <v>65.9121466709565</v>
+        <v>-0.0448746789209971</v>
       </c>
     </row>
     <row r="921" spans="1:4">
@@ -14472,7 +14472,7 @@
         <v>139</v>
       </c>
       <c r="D921">
-        <v>64.878732641287</v>
+        <v>-2.85302788216353</v>
       </c>
     </row>
     <row r="922" spans="1:4">
@@ -14486,7 +14486,7 @@
         <v>140</v>
       </c>
       <c r="D922">
-        <v>66.1327005813849</v>
+        <v>0.256244830934605</v>
       </c>
     </row>
     <row r="923" spans="1:4">
@@ -14500,7 +14500,7 @@
         <v>141</v>
       </c>
       <c r="D923">
-        <v>69.7582036769373</v>
+        <v>5.78978723520342</v>
       </c>
     </row>
     <row r="924" spans="1:4">
@@ -14514,7 +14514,7 @@
         <v>142</v>
       </c>
       <c r="D924">
-        <v>68.5514090741744</v>
+        <v>1.65228962923914</v>
       </c>
     </row>
     <row r="925" spans="1:4">
@@ -14528,7 +14528,7 @@
         <v>143</v>
       </c>
       <c r="D925">
-        <v>70.0702200077162</v>
+        <v>6.00414983458767</v>
       </c>
     </row>
     <row r="926" spans="1:4">
@@ -14542,7 +14542,7 @@
         <v>144</v>
       </c>
       <c r="D926">
-        <v>70.4785261899396</v>
+        <v>5.4591600696252</v>
       </c>
     </row>
     <row r="927" spans="1:4">
@@ -14556,7 +14556,7 @@
         <v>145</v>
       </c>
       <c r="D927">
-        <v>70.3311169498805</v>
+        <v>6.75933094380821</v>
       </c>
     </row>
     <row r="928" spans="1:4">
@@ -14570,7 +14570,7 @@
         <v>146</v>
       </c>
       <c r="D928">
-        <v>70.776206632412</v>
+        <v>6.36469702155142</v>
       </c>
     </row>
     <row r="929" spans="1:4">
@@ -14584,7 +14584,7 @@
         <v>147</v>
       </c>
       <c r="D929">
-        <v>70.22270064921049</v>
+        <v>5.77168742091727</v>
       </c>
     </row>
     <row r="930" spans="1:4">
@@ -14598,7 +14598,7 @@
         <v>148</v>
       </c>
       <c r="D930">
-        <v>69.2773786354421</v>
+        <v>4.31619682413954</v>
       </c>
     </row>
     <row r="931" spans="1:4">
@@ -14612,7 +14612,7 @@
         <v>149</v>
       </c>
       <c r="D931">
-        <v>70.0079067628718</v>
+        <v>7.90109079861929</v>
       </c>
     </row>
     <row r="932" spans="1:4">
@@ -14626,7 +14626,7 @@
         <v>150</v>
       </c>
       <c r="D932">
-        <v>71.11439034683779</v>
+        <v>7.89269343911933</v>
       </c>
     </row>
     <row r="933" spans="1:4">
@@ -14640,7 +14640,7 @@
         <v>151</v>
       </c>
       <c r="D933">
-        <v>71.66106894637331</v>
+        <v>10.4538668204043</v>
       </c>
     </row>
     <row r="934" spans="1:4">
@@ -14654,7 +14654,7 @@
         <v>152</v>
       </c>
       <c r="D934">
-        <v>71.537981490563</v>
+        <v>8.173386027879211</v>
       </c>
     </row>
     <row r="935" spans="1:4">
@@ -14668,7 +14668,7 @@
         <v>153</v>
       </c>
       <c r="D935">
-        <v>73.2005539681292</v>
+        <v>4.93468883908485</v>
       </c>
     </row>
     <row r="936" spans="1:4">
@@ -14682,7 +14682,7 @@
         <v>154</v>
       </c>
       <c r="D936">
-        <v>71.8349587866558</v>
+        <v>4.78990841592843</v>
       </c>
     </row>
     <row r="937" spans="1:4">
@@ -14696,7 +14696,7 @@
         <v>155</v>
       </c>
       <c r="D937">
-        <v>73.3269495913511</v>
+        <v>4.64780841743648</v>
       </c>
     </row>
     <row r="938" spans="1:4">
@@ -14710,7 +14710,7 @@
         <v>156</v>
       </c>
       <c r="D938">
-        <v>71.8830609752045</v>
+        <v>1.99285493212454</v>
       </c>
     </row>
     <row r="939" spans="1:4">
@@ -14724,7 +14724,7 @@
         <v>157</v>
       </c>
       <c r="D939">
-        <v>72.6760506917521</v>
+        <v>3.33413408398256</v>
       </c>
     </row>
     <row r="940" spans="1:4">
@@ -14738,7 +14738,7 @@
         <v>158</v>
       </c>
       <c r="D940">
-        <v>73.1026225236203</v>
+        <v>3.2870027964213</v>
       </c>
     </row>
     <row r="941" spans="1:4">
@@ -14752,7 +14752,7 @@
         <v>159</v>
       </c>
       <c r="D941">
-        <v>72.4678343612086</v>
+        <v>3.1971623011388</v>
       </c>
     </row>
     <row r="942" spans="1:4">
@@ -14766,7 +14766,7 @@
         <v>160</v>
       </c>
       <c r="D942">
-        <v>73.62593116709169</v>
+        <v>6.27701656341957</v>
       </c>
     </row>
     <row r="943" spans="1:4">
@@ -14780,7 +14780,7 @@
         <v>161</v>
       </c>
       <c r="D943">
-        <v>74.27465749508249</v>
+        <v>6.09466977303418</v>
       </c>
     </row>
     <row r="944" spans="1:4">
@@ -14794,7 +14794,7 @@
         <v>162</v>
       </c>
       <c r="D944">
-        <v>74.5722561840256</v>
+        <v>4.86239960762255</v>
       </c>
     </row>
     <row r="945" spans="1:4">
@@ -14808,7 +14808,7 @@
         <v>163</v>
       </c>
       <c r="D945">
-        <v>76.8335741669796</v>
+        <v>7.21801292760101</v>
       </c>
     </row>
     <row r="946" spans="1:4">
@@ -14822,7 +14822,7 @@
         <v>164</v>
       </c>
       <c r="D946">
-        <v>77.84676571068481</v>
+        <v>8.81878980741725</v>
       </c>
     </row>
     <row r="947" spans="1:4">
@@ -14836,7 +14836,7 @@
         <v>165</v>
       </c>
       <c r="D947">
-        <v>78.6915107380435</v>
+        <v>7.50125029423277</v>
       </c>
     </row>
     <row r="948" spans="1:4">
@@ -14850,7 +14850,7 @@
         <v>166</v>
       </c>
       <c r="D948">
-        <v>77.7818039607597</v>
+        <v>8.27848344949367</v>
       </c>
     </row>
     <row r="949" spans="1:4">
@@ -14864,7 +14864,7 @@
         <v>167</v>
       </c>
       <c r="D949">
-        <v>79.7014181472407</v>
+        <v>8.69321387486365</v>
       </c>
     </row>
     <row r="950" spans="1:4">
@@ -14878,7 +14878,7 @@
         <v>168</v>
       </c>
       <c r="D950">
-        <v>80.44396131795951</v>
+        <v>11.9094821876158</v>
       </c>
     </row>
     <row r="951" spans="1:4">
@@ -14892,7 +14892,7 @@
         <v>169</v>
       </c>
       <c r="D951">
-        <v>80.73141090355929</v>
+        <v>11.0839267339569</v>
       </c>
     </row>
     <row r="952" spans="1:4">
@@ -14906,7 +14906,7 @@
         <v>170</v>
       </c>
       <c r="D952">
-        <v>80.56775317209259</v>
+        <v>10.2118506706927</v>
       </c>
     </row>
     <row r="953" spans="1:4">
@@ -14920,7 +14920,7 @@
         <v>171</v>
       </c>
       <c r="D953">
-        <v>81.1539327713579</v>
+        <v>11.9861432133522</v>
       </c>
     </row>
     <row r="954" spans="1:4">
@@ -14934,7 +14934,7 @@
         <v>172</v>
       </c>
       <c r="D954">
-        <v>82.5775106672657</v>
+        <v>12.1581885054312</v>
       </c>
     </row>
     <row r="955" spans="1:4">
@@ -14948,7 +14948,7 @@
         <v>173</v>
       </c>
       <c r="D955">
-        <v>83.4247285684568</v>
+        <v>12.3192369806352</v>
       </c>
     </row>
     <row r="956" spans="1:4">
@@ -14962,7 +14962,7 @@
         <v>174</v>
       </c>
       <c r="D956">
-        <v>82.2569632085338</v>
+        <v>10.305048308508</v>
       </c>
     </row>
     <row r="957" spans="1:4">
@@ -14976,7 +14976,7 @@
         <v>175</v>
       </c>
       <c r="D957">
-        <v>82.45837033148661</v>
+        <v>7.3207529722395</v>
       </c>
     </row>
     <row r="958" spans="1:4">
@@ -14990,7 +14990,7 @@
         <v>176</v>
       </c>
       <c r="D958">
-        <v>83.2648460221543</v>
+        <v>6.9599298853412</v>
       </c>
     </row>
     <row r="959" spans="1:4">
@@ -15004,7 +15004,7 @@
         <v>177</v>
       </c>
       <c r="D959">
-        <v>81.23538758445591</v>
+        <v>3.23272081391438</v>
       </c>
     </row>
     <row r="960" spans="1:4">
@@ -15018,7 +15018,7 @@
         <v>178</v>
       </c>
       <c r="D960">
-        <v>83.2374508447472</v>
+        <v>7.01404005330068</v>
       </c>
     </row>
     <row r="961" spans="1:4">
@@ -15032,7 +15032,7 @@
         <v>179</v>
       </c>
       <c r="D961">
-        <v>83.6597387915189</v>
+        <v>4.96643690450474</v>
       </c>
     </row>
     <row r="962" spans="1:4">
@@ -15046,7 +15046,7 @@
         <v>180</v>
       </c>
       <c r="D962">
-        <v>84.9411372456638</v>
+        <v>5.59044563945445</v>
       </c>
     </row>
     <row r="963" spans="1:4">
@@ -15060,7 +15060,7 @@
         <v>181</v>
       </c>
       <c r="D963">
-        <v>85.1322904480058</v>
+        <v>5.45126053811167</v>
       </c>
     </row>
     <row r="964" spans="1:4">
@@ -15074,7 +15074,7 @@
         <v>182</v>
       </c>
       <c r="D964">
-        <v>83.5906371538686</v>
+        <v>3.75197751303692</v>
       </c>
     </row>
     <row r="965" spans="1:4">
@@ -15088,7 +15088,7 @@
         <v>183</v>
       </c>
       <c r="D965">
-        <v>86.7527843782716</v>
+        <v>6.89905148859247</v>
       </c>
     </row>
     <row r="966" spans="1:4">
@@ -15102,7 +15102,7 @@
         <v>184</v>
       </c>
       <c r="D966">
-        <v>87.7804371181968</v>
+        <v>6.30065790175675</v>
       </c>
     </row>
     <row r="967" spans="1:4">
@@ -15116,7 +15116,7 @@
         <v>185</v>
       </c>
       <c r="D967">
-        <v>92.69119443097649</v>
+        <v>11.1075768798166</v>
       </c>
     </row>
     <row r="968" spans="1:4">
@@ -15130,7 +15130,7 @@
         <v>186</v>
       </c>
       <c r="D968">
-        <v>90.4147381346862</v>
+        <v>9.9174277872029</v>
       </c>
     </row>
     <row r="969" spans="1:4">
@@ -15144,7 +15144,7 @@
         <v>187</v>
       </c>
       <c r="D969">
-        <v>90.9633132013663</v>
+        <v>10.3142262400887</v>
       </c>
     </row>
     <row r="970" spans="1:4">
@@ -15158,7 +15158,7 @@
         <v>188</v>
       </c>
       <c r="D970">
-        <v>90.5443643945294</v>
+        <v>8.74260713871762</v>
       </c>
     </row>
     <row r="971" spans="1:4">
@@ -15172,7 +15172,7 @@
         <v>189</v>
       </c>
       <c r="D971">
-        <v>91.98514900608821</v>
+        <v>13.2328554602591</v>
       </c>
     </row>
     <row r="972" spans="1:4">
@@ -15186,7 +15186,7 @@
         <v>190</v>
       </c>
       <c r="D972">
-        <v>94.23092156962539</v>
+        <v>13.2073611256825</v>
       </c>
     </row>
     <row r="973" spans="1:4">
@@ -15200,7 +15200,7 @@
         <v>191</v>
       </c>
       <c r="D973">
-        <v>92.4447290059089</v>
+        <v>10.5008578096117</v>
       </c>
     </row>
     <row r="974" spans="1:4">
@@ -15214,7 +15214,7 @@
         <v>192</v>
       </c>
       <c r="D974">
-        <v>93.01948935219021</v>
+        <v>9.510529725028849</v>
       </c>
     </row>
     <row r="975" spans="1:4">
@@ -15228,7 +15228,7 @@
         <v>193</v>
       </c>
       <c r="D975">
-        <v>95.09678808161161</v>
+        <v>11.7047216528158</v>
       </c>
     </row>
     <row r="976" spans="1:4">
@@ -15242,7 +15242,7 @@
         <v>194</v>
       </c>
       <c r="D976">
-        <v>96.18141850035541</v>
+        <v>15.0624301658456</v>
       </c>
     </row>
     <row r="977" spans="1:4">
@@ -15256,7 +15256,7 @@
         <v>195</v>
       </c>
       <c r="D977">
-        <v>97.70284237250991</v>
+        <v>12.6221401107915</v>
       </c>
     </row>
     <row r="978" spans="1:4">
@@ -15270,7 +15270,7 @@
         <v>196</v>
       </c>
       <c r="D978">
-        <v>92.9079470774392</v>
+        <v>5.84129007279627</v>
       </c>
     </row>
     <row r="979" spans="1:4">
@@ -15284,7 +15284,7 @@
         <v>197</v>
       </c>
       <c r="D979">
-        <v>91.0630551953891</v>
+        <v>-1.75651985669449</v>
       </c>
     </row>
     <row r="980" spans="1:4">
@@ -15298,7 +15298,7 @@
         <v>198</v>
       </c>
       <c r="D980">
-        <v>91.210884940684</v>
+        <v>0.880549811261759</v>
       </c>
     </row>
     <row r="981" spans="1:4">
@@ -15312,7 +15312,7 @@
         <v>199</v>
       </c>
       <c r="D981">
-        <v>89.755015659976</v>
+        <v>-1.32833501646481</v>
       </c>
     </row>
     <row r="982" spans="1:4">
@@ -15326,7 +15326,7 @@
         <v>200</v>
       </c>
       <c r="D982">
-        <v>85.6882571921944</v>
+        <v>-5.36323517737168</v>
       </c>
     </row>
     <row r="983" spans="1:4">
@@ -15340,7 +15340,7 @@
         <v>201</v>
       </c>
       <c r="D983">
-        <v>81.6343392168029</v>
+        <v>-11.2526966593273</v>
       </c>
     </row>
     <row r="984" spans="1:4">
@@ -15354,7 +15354,7 @@
         <v>202</v>
       </c>
       <c r="D984">
-        <v>80.9840750522454</v>
+        <v>-14.0578552100779</v>
       </c>
     </row>
     <row r="985" spans="1:4">
@@ -15368,7 +15368,7 @@
         <v>203</v>
       </c>
       <c r="D985">
-        <v>80.74552365654731</v>
+        <v>-12.6553514463911</v>
       </c>
     </row>
     <row r="986" spans="1:4">
@@ -15382,7 +15382,7 @@
         <v>204</v>
       </c>
       <c r="D986">
-        <v>80.15358626223259</v>
+        <v>-13.831405847913</v>
       </c>
     </row>
     <row r="987" spans="1:4">
@@ -15396,7 +15396,7 @@
         <v>205</v>
       </c>
       <c r="D987">
-        <v>80.3133487335954</v>
+        <v>-15.5456768269914</v>
       </c>
     </row>
     <row r="988" spans="1:4">
@@ -15410,7 +15410,7 @@
         <v>206</v>
       </c>
       <c r="D988">
-        <v>81.459215988293</v>
+        <v>-15.3067013791318</v>
       </c>
     </row>
     <row r="989" spans="1:4">
@@ -15424,7 +15424,7 @@
         <v>207</v>
       </c>
       <c r="D989">
-        <v>83.007646109978</v>
+        <v>-15.040704963837</v>
       </c>
     </row>
     <row r="990" spans="1:4">
@@ -15438,7 +15438,7 @@
         <v>208</v>
       </c>
       <c r="D990">
-        <v>81.0850189282925</v>
+        <v>-12.7254217976555</v>
       </c>
     </row>
     <row r="991" spans="1:4">
@@ -15452,7 +15452,7 @@
         <v>209</v>
       </c>
       <c r="D991">
-        <v>82.01115865942759</v>
+        <v>-9.9402513088753</v>
       </c>
     </row>
     <row r="992" spans="1:4">
@@ -15466,7 +15466,7 @@
         <v>210</v>
       </c>
       <c r="D992">
-        <v>81.5250290038622</v>
+        <v>-10.6191886452156</v>
       </c>
     </row>
     <row r="993" spans="1:4">
@@ -15480,7 +15480,7 @@
         <v>211</v>
       </c>
       <c r="D993">
-        <v>81.3198621777403</v>
+        <v>-9.397974497816429</v>
       </c>
     </row>
     <row r="994" spans="1:4">
@@ -15494,7 +15494,7 @@
         <v>212</v>
       </c>
       <c r="D994">
-        <v>83.18589369269689</v>
+        <v>-2.92031088213736</v>
       </c>
     </row>
     <row r="995" spans="1:4">
@@ -15508,7 +15508,7 @@
         <v>213</v>
       </c>
       <c r="D995">
-        <v>84.3403606665759</v>
+        <v>3.3148078072714</v>
       </c>
     </row>
     <row r="996" spans="1:4">
@@ -15522,7 +15522,7 @@
         <v>214</v>
       </c>
       <c r="D996">
-        <v>83.82561384904371</v>
+        <v>3.50876242639696</v>
       </c>
     </row>
     <row r="997" spans="1:4">
@@ -15536,7 +15536,7 @@
         <v>215</v>
       </c>
       <c r="D997">
-        <v>86.0914806819822</v>
+        <v>6.62074723569078</v>
       </c>
     </row>
     <row r="998" spans="1:4">
@@ -15550,7 +15550,7 @@
         <v>216</v>
       </c>
       <c r="D998">
-        <v>87.1934703588484</v>
+        <v>8.78299328190249</v>
       </c>
     </row>
     <row r="999" spans="1:4">
@@ -15564,7 +15564,7 @@
         <v>217</v>
       </c>
       <c r="D999">
-        <v>85.3476238859602</v>
+        <v>6.26829192375456</v>
       </c>
     </row>
     <row r="1000" spans="1:4">
@@ -15578,7 +15578,7 @@
         <v>218</v>
       </c>
       <c r="D1000">
-        <v>85.91979947754</v>
+        <v>5.47584878534561</v>
       </c>
     </row>
     <row r="1001" spans="1:4">
@@ -15592,7 +15592,7 @@
         <v>219</v>
       </c>
       <c r="D1001">
-        <v>84.2093572345547</v>
+        <v>1.44771136261898</v>
       </c>
     </row>
     <row r="1002" spans="1:4">
@@ -15606,7 +15606,7 @@
         <v>220</v>
       </c>
       <c r="D1002">
-        <v>86.1229928270195</v>
+        <v>6.21319938666147</v>
       </c>
     </row>
     <row r="1003" spans="1:4">
@@ -15620,7 +15620,7 @@
         <v>221</v>
       </c>
       <c r="D1003">
-        <v>87.06207191550619</v>
+        <v>6.15881221365719</v>
       </c>
     </row>
     <row r="1004" spans="1:4">
@@ -15634,7 +15634,7 @@
         <v>222</v>
       </c>
       <c r="D1004">
-        <v>88.26519276319129</v>
+        <v>8.26760056596825</v>
       </c>
     </row>
     <row r="1005" spans="1:4">
@@ -15648,7 +15648,7 @@
         <v>223</v>
       </c>
       <c r="D1005">
-        <v>88.4750727256078</v>
+        <v>8.79884736182705</v>
       </c>
     </row>
     <row r="1006" spans="1:4">
@@ -15662,7 +15662,7 @@
         <v>224</v>
       </c>
       <c r="D1006">
-        <v>89.4308524798237</v>
+        <v>7.50723290921988</v>
       </c>
     </row>
     <row r="1007" spans="1:4">
@@ -15676,7 +15676,7 @@
         <v>225</v>
       </c>
       <c r="D1007">
-        <v>91.2128693645455</v>
+        <v>8.14854079784979</v>
       </c>
     </row>
     <row r="1008" spans="1:4">
@@ -15690,7 +15690,7 @@
         <v>226</v>
       </c>
       <c r="D1008">
-        <v>88.94822379386891</v>
+        <v>6.11103183097494</v>
       </c>
     </row>
     <row r="1009" spans="1:4">
@@ -15704,7 +15704,7 @@
         <v>227</v>
       </c>
       <c r="D1009">
-        <v>88.4444452200883</v>
+        <v>2.73309800164529</v>
       </c>
     </row>
     <row r="1010" spans="1:4">
@@ -15718,7 +15718,7 @@
         <v>228</v>
       </c>
       <c r="D1010">
-        <v>89.7607425025876</v>
+        <v>2.94433990661627</v>
       </c>
     </row>
     <row r="1011" spans="1:4">
@@ -15732,7 +15732,7 @@
         <v>229</v>
       </c>
       <c r="D1011">
-        <v>92.2855789937028</v>
+        <v>8.129054790105171</v>
       </c>
     </row>
     <row r="1012" spans="1:4">
@@ -15746,7 +15746,7 @@
         <v>230</v>
       </c>
       <c r="D1012">
-        <v>95.7767711415394</v>
+        <v>11.4722936086182</v>
       </c>
     </row>
     <row r="1013" spans="1:4">
@@ -15760,7 +15760,7 @@
         <v>231</v>
       </c>
       <c r="D1013">
-        <v>94.6416274685008</v>
+        <v>12.3884928902715</v>
       </c>
     </row>
     <row r="1014" spans="1:4">
@@ -15774,7 +15774,7 @@
         <v>232</v>
       </c>
       <c r="D1014">
-        <v>96.758285245278</v>
+        <v>12.3489582388524</v>
       </c>
     </row>
     <row r="1015" spans="1:4">
@@ -15788,7 +15788,7 @@
         <v>233</v>
       </c>
       <c r="D1015">
-        <v>94.635056764932</v>
+        <v>8.69837425506643</v>
       </c>
     </row>
     <row r="1016" spans="1:4">
@@ -15802,7 +15802,7 @@
         <v>234</v>
       </c>
       <c r="D1016">
-        <v>96.5647479360471</v>
+        <v>9.40297631833521</v>
       </c>
     </row>
     <row r="1017" spans="1:4">
@@ -15816,7 +15816,7 @@
         <v>235</v>
       </c>
       <c r="D1017">
-        <v>97.3764996736768</v>
+        <v>10.0609433525706</v>
       </c>
     </row>
     <row r="1018" spans="1:4">
@@ -15830,7 +15830,7 @@
         <v>236</v>
       </c>
       <c r="D1018">
-        <v>98.8858718304146</v>
+        <v>10.5724356733869</v>
       </c>
     </row>
     <row r="1019" spans="1:4">
@@ -15844,7 +15844,7 @@
         <v>237</v>
       </c>
       <c r="D1019">
-        <v>96.9027910688025</v>
+        <v>6.23806897414487</v>
       </c>
     </row>
     <row r="1020" spans="1:4">
@@ -15858,7 +15858,7 @@
         <v>238</v>
       </c>
       <c r="D1020">
-        <v>97.12379088603871</v>
+        <v>9.191377571648969</v>
       </c>
     </row>
     <row r="1021" spans="1:4">
@@ -15872,7 +15872,7 @@
         <v>239</v>
       </c>
       <c r="D1021">
-        <v>96.3267951895625</v>
+        <v>8.912204661196631</v>
       </c>
     </row>
     <row r="1022" spans="1:4">
@@ -15886,7 +15886,7 @@
         <v>240</v>
       </c>
       <c r="D1022">
-        <v>98.6853511988698</v>
+        <v>9.94266362716966</v>
       </c>
     </row>
     <row r="1023" spans="1:4">
@@ -15900,7 +15900,7 @@
         <v>241</v>
       </c>
       <c r="D1023">
-        <v>98.0864328900434</v>
+        <v>6.28576421104366</v>
       </c>
     </row>
     <row r="1024" spans="1:4">
@@ -15914,7 +15914,7 @@
         <v>242</v>
       </c>
       <c r="D1024">
-        <v>96.5229522218423</v>
+        <v>0.779083562130314</v>
       </c>
     </row>
     <row r="1025" spans="1:4">
@@ -15928,7 +15928,7 @@
         <v>243</v>
       </c>
       <c r="D1025">
-        <v>99.60240773843221</v>
+        <v>5.24164725673434</v>
       </c>
     </row>
     <row r="1026" spans="1:4">
@@ -15942,7 +15942,7 @@
         <v>244</v>
       </c>
       <c r="D1026">
-        <v>97.2835291224862</v>
+        <v>0.542841241839629</v>
       </c>
     </row>
     <row r="1027" spans="1:4">
@@ -15956,7 +15956,7 @@
         <v>245</v>
       </c>
       <c r="D1027">
-        <v>99.58879539833789</v>
+        <v>5.23457036192274</v>
       </c>
     </row>
     <row r="1028" spans="1:4">
@@ -15970,7 +15970,7 @@
         <v>246</v>
       </c>
       <c r="D1028">
-        <v>97.06438811012561</v>
+        <v>0.517414672287457</v>
       </c>
     </row>
     <row r="1029" spans="1:4">
@@ -15984,7 +15984,7 @@
         <v>247</v>
       </c>
       <c r="D1029">
-        <v>98.1179187747699</v>
+        <v>0.761394282581225</v>
       </c>
     </row>
     <row r="1030" spans="1:4">
@@ -15998,7 +15998,7 @@
         <v>248</v>
       </c>
       <c r="D1030">
-        <v>94.27343437066951</v>
+        <v>-4.66440490877731</v>
       </c>
     </row>
     <row r="1031" spans="1:4">
@@ -16012,7 +16012,7 @@
         <v>249</v>
       </c>
       <c r="D1031">
-        <v>94.6602424125854</v>
+        <v>-2.31422504087096</v>
       </c>
     </row>
     <row r="1032" spans="1:4">
@@ -16026,7 +16026,7 @@
         <v>250</v>
       </c>
       <c r="D1032">
-        <v>96.9890824170492</v>
+        <v>-0.138697705022205</v>
       </c>
     </row>
     <row r="1033" spans="1:4">
@@ -16040,7 +16040,7 @@
         <v>251</v>
       </c>
       <c r="D1033">
-        <v>96.323488301975</v>
+        <v>-0.00343298827807071</v>
       </c>
     </row>
     <row r="1034" spans="1:4">
@@ -16054,7 +16054,7 @@
         <v>252</v>
       </c>
       <c r="D1034">
-        <v>93.4610271563147</v>
+        <v>-5.29392050500696</v>
       </c>
     </row>
     <row r="1035" spans="1:4">
@@ -16068,7 +16068,7 @@
         <v>253</v>
       </c>
       <c r="D1035">
-        <v>95.0663410016555</v>
+        <v>-3.07901082688313</v>
       </c>
     </row>
     <row r="1036" spans="1:4">
@@ -16082,7 +16082,7 @@
         <v>254</v>
       </c>
       <c r="D1036">
-        <v>91.7724482620095</v>
+        <v>-4.92163143633914</v>
       </c>
     </row>
     <row r="1037" spans="1:4">
@@ -16096,7 +16096,7 @@
         <v>255</v>
       </c>
       <c r="D1037">
-        <v>93.7272095674053</v>
+        <v>-5.8986507499456</v>
       </c>
     </row>
     <row r="1038" spans="1:4">
@@ -16110,7 +16110,7 @@
         <v>256</v>
       </c>
       <c r="D1038">
-        <v>91.7716616374716</v>
+        <v>-5.66577665791175</v>
       </c>
     </row>
     <row r="1039" spans="1:4">
@@ -16124,7 +16124,7 @@
         <v>257</v>
       </c>
       <c r="D1039">
-        <v>91.5791534254497</v>
+        <v>-8.042713982884329</v>
       </c>
     </row>
     <row r="1040" spans="1:4">
@@ -16138,7 +16138,7 @@
         <v>258</v>
       </c>
       <c r="D1040">
-        <v>91.95983727471911</v>
+        <v>-5.25893268869636</v>
       </c>
     </row>
     <row r="1041" spans="1:4">
@@ -16152,7 +16152,7 @@
         <v>259</v>
       </c>
       <c r="D1041">
-        <v>90.9972282293605</v>
+        <v>-7.25727842001518</v>
       </c>
     </row>
     <row r="1042" spans="1:4">
@@ -16166,7 +16166,7 @@
         <v>260</v>
       </c>
       <c r="D1042">
-        <v>93.92053808415341</v>
+        <v>-0.374332693904586</v>
       </c>
     </row>
     <row r="1043" spans="1:4">
@@ -16180,7 +16180,7 @@
         <v>261</v>
       </c>
       <c r="D1043">
-        <v>91.7236345761419</v>
+        <v>-3.10226105659441</v>
       </c>
     </row>
     <row r="1044" spans="1:4">
@@ -16194,7 +16194,7 @@
         <v>262</v>
       </c>
       <c r="D1044">
-        <v>94.6636917496956</v>
+        <v>-2.39757981971055</v>
       </c>
     </row>
     <row r="1045" spans="1:4">
@@ -16208,7 +16208,7 @@
         <v>263</v>
       </c>
       <c r="D1045">
-        <v>95.5629882460256</v>
+        <v>-0.789527112603348</v>
       </c>
     </row>
     <row r="1046" spans="1:4">
@@ -16222,7 +16222,7 @@
         <v>264</v>
       </c>
       <c r="D1046">
-        <v>95.507603021837</v>
+        <v>2.18976393454287</v>
       </c>
     </row>
     <row r="1047" spans="1:4">
@@ -16236,7 +16236,7 @@
         <v>265</v>
       </c>
       <c r="D1047">
-        <v>95.22184115060671</v>
+        <v>0.163570141979586</v>
       </c>
     </row>
     <row r="1048" spans="1:4">
@@ -16250,7 +16250,7 @@
         <v>266</v>
       </c>
       <c r="D1048">
-        <v>95.72301369498651</v>
+        <v>4.3047401565426</v>
       </c>
     </row>
     <row r="1049" spans="1:4">
@@ -16264,7 +16264,7 @@
         <v>267</v>
       </c>
       <c r="D1049">
-        <v>94.28600671446419</v>
+        <v>0.596195224031533</v>
       </c>
     </row>
     <row r="1050" spans="1:4">
@@ -16278,7 +16278,7 @@
         <v>268</v>
       </c>
       <c r="D1050">
-        <v>95.49804096883931</v>
+        <v>4.06049020457768</v>
       </c>
     </row>
     <row r="1051" spans="1:4">
@@ -16292,7 +16292,7 @@
         <v>269</v>
       </c>
       <c r="D1051">
-        <v>94.5595647161522</v>
+        <v>3.25446477634094</v>
       </c>
     </row>
     <row r="1052" spans="1:4">
@@ -16306,7 +16306,7 @@
         <v>270</v>
       </c>
       <c r="D1052">
-        <v>98.9509989134112</v>
+        <v>7.60240757909002</v>
       </c>
     </row>
     <row r="1053" spans="1:4">
@@ -16320,7 +16320,7 @@
         <v>271</v>
       </c>
       <c r="D1053">
-        <v>98.2569472992914</v>
+        <v>7.97795626437392</v>
       </c>
     </row>
     <row r="1054" spans="1:4">
@@ -16334,7 +16334,7 @@
         <v>272</v>
       </c>
       <c r="D1054">
-        <v>97.9481053244868</v>
+        <v>4.28827104538591</v>
       </c>
     </row>
     <row r="1055" spans="1:4">
@@ -16348,7 +16348,7 @@
         <v>273</v>
       </c>
       <c r="D1055">
-        <v>99.1570644002209</v>
+        <v>8.104159694967541</v>
       </c>
     </row>
     <row r="1056" spans="1:4">
@@ -16362,7 +16362,7 @@
         <v>274</v>
       </c>
       <c r="D1056">
-        <v>96.16864341838669</v>
+        <v>1.58978763755633</v>
       </c>
     </row>
     <row r="1057" spans="1:4">
@@ -16376,7 +16376,7 @@
         <v>275</v>
       </c>
       <c r="D1057">
-        <v>97.2137389994855</v>
+        <v>1.7273954945926</v>
       </c>
     </row>
     <row r="1058" spans="1:4">
@@ -16390,7 +16390,7 @@
         <v>276</v>
       </c>
       <c r="D1058">
-        <v>100.753509371037</v>
+        <v>5.49265836773285</v>
       </c>
     </row>
     <row r="1059" spans="1:4">
@@ -16404,7 +16404,7 @@
         <v>277</v>
       </c>
       <c r="D1059">
-        <v>98.6515618182563</v>
+        <v>3.60182141639648</v>
       </c>
     </row>
     <row r="1060" spans="1:4">
@@ -16418,7 +16418,7 @@
         <v>278</v>
       </c>
       <c r="D1060">
-        <v>100.811888947224</v>
+        <v>5.316250560657</v>
       </c>
     </row>
     <row r="1061" spans="1:4">
@@ -16432,7 +16432,7 @@
         <v>279</v>
       </c>
       <c r="D1061">
-        <v>102.701554583263</v>
+        <v>8.925553390212469</v>
       </c>
     </row>
     <row r="1062" spans="1:4">
@@ -16446,7 +16446,7 @@
         <v>280</v>
       </c>
       <c r="D1062">
-        <v>102.201369407125</v>
+        <v>7.0193360725305</v>
       </c>
     </row>
     <row r="1063" spans="1:4">
@@ -16460,7 +16460,7 @@
         <v>281</v>
       </c>
       <c r="D1063">
-        <v>103.325379780717</v>
+        <v>9.270151666706511</v>
       </c>
     </row>
     <row r="1064" spans="1:4">
@@ -16474,7 +16474,7 @@
         <v>282</v>
       </c>
       <c r="D1064">
-        <v>99.7431124841961</v>
+        <v>0.800510939235751</v>
       </c>
     </row>
     <row r="1065" spans="1:4">
@@ -16488,7 +16488,7 @@
         <v>283</v>
       </c>
       <c r="D1065">
-        <v>100.976188202309</v>
+        <v>2.76747952970163</v>
       </c>
     </row>
     <row r="1066" spans="1:4">
@@ -16502,7 +16502,7 @@
         <v>284</v>
       </c>
       <c r="D1066">
-        <v>98.6891734091768</v>
+        <v>0.756592567293626</v>
       </c>
     </row>
     <row r="1067" spans="1:4">
@@ -16516,7 +16516,7 @@
         <v>285</v>
       </c>
       <c r="D1067">
-        <v>99.429409729715</v>
+        <v>0.274660540972504</v>
       </c>
     </row>
     <row r="1068" spans="1:4">
@@ -16530,7 +16530,7 @@
         <v>286</v>
       </c>
       <c r="D1068">
-        <v>101.309699467421</v>
+        <v>5.34587560590605</v>
       </c>
     </row>
     <row r="1069" spans="1:4">
@@ -16544,7 +16544,7 @@
         <v>287</v>
       </c>
       <c r="D1069">
-        <v>99.7100388941839</v>
+        <v>2.56784680888738</v>
       </c>
     </row>
     <row r="1070" spans="1:4">
@@ -16558,7 +16558,7 @@
         <v>288</v>
       </c>
       <c r="D1070">
-        <v>99.8159349489819</v>
+        <v>-0.930562546067117</v>
       </c>
     </row>
     <row r="1071" spans="1:4">
@@ -16572,7 +16572,7 @@
         <v>289</v>
       </c>
       <c r="D1071">
-        <v>98.69491923031779</v>
+        <v>0.0439500513345879</v>
       </c>
     </row>
     <row r="1072" spans="1:4">
@@ -16586,7 +16586,7 @@
         <v>290</v>
       </c>
       <c r="D1072">
-        <v>99.2742638690177</v>
+        <v>-1.52524180854429</v>
       </c>
     </row>
     <row r="1073" spans="1:4">
@@ -16600,7 +16600,7 @@
         <v>291</v>
       </c>
       <c r="D1073">
-        <v>97.4952129190726</v>
+        <v>-5.06938934402349</v>
       </c>
     </row>
     <row r="1074" spans="1:4">
@@ -16614,7 +16614,7 @@
         <v>292</v>
       </c>
       <c r="D1074">
-        <v>100.731629099938</v>
+        <v>-1.43808279254283</v>
       </c>
     </row>
     <row r="1075" spans="1:4">
@@ -16628,7 +16628,7 @@
         <v>293</v>
       </c>
       <c r="D1075">
-        <v>100.4722637887</v>
+        <v>-2.76129252858498</v>
       </c>
     </row>
     <row r="1076" spans="1:4">
@@ -16642,7 +16642,7 @@
         <v>294</v>
       </c>
       <c r="D1076">
-        <v>101.755561004835</v>
+        <v>2.01763156424236</v>
       </c>
     </row>
     <row r="1077" spans="1:4">
@@ -16656,7 +16656,7 @@
         <v>295</v>
       </c>
       <c r="D1077">
-        <v>103.13646577198</v>
+        <v>2.13939306695041</v>
       </c>
     </row>
     <row r="1078" spans="1:4">
@@ -16670,7 +16670,7 @@
         <v>296</v>
       </c>
       <c r="D1078">
-        <v>102.838195966591</v>
+        <v>4.20413143011328</v>
       </c>
     </row>
     <row r="1079" spans="1:4">
@@ -16684,7 +16684,7 @@
         <v>297</v>
       </c>
       <c r="D1079">
-        <v>100.886603643221</v>
+        <v>1.46555623478724</v>
       </c>
     </row>
     <row r="1080" spans="1:4">
@@ -16698,7 +16698,7 @@
         <v>298</v>
       </c>
       <c r="D1080">
-        <v>99.4627459962926</v>
+        <v>-1.823076646005</v>
       </c>
     </row>
     <row r="1081" spans="1:4">
@@ -16712,7 +16712,7 @@
         <v>299</v>
       </c>
       <c r="D1081">
-        <v>100.425595680062</v>
+        <v>0.717637655961084</v>
       </c>
     </row>
     <row r="1082" spans="1:4">
@@ -16726,7 +16726,7 @@
         <v>300</v>
       </c>
       <c r="D1082">
-        <v>97.2793543346253</v>
+        <v>-2.54125818252678</v>
       </c>
     </row>
     <row r="1083" spans="1:4">
@@ -16740,7 +16740,7 @@
         <v>301</v>
       </c>
       <c r="D1083">
-        <v>99.6452774653993</v>
+        <v>0.962925186517172</v>
       </c>
     </row>
     <row r="1084" spans="1:4">
@@ -16754,7 +16754,7 @@
         <v>302</v>
       </c>
       <c r="D1084">
-        <v>100.484980550904</v>
+        <v>1.21956752405005</v>
       </c>
     </row>
     <row r="1085" spans="1:4">
@@ -16768,7 +16768,7 @@
         <v>303</v>
       </c>
       <c r="D1085">
-        <v>99.1788367553262</v>
+        <v>1.72687846494691</v>
       </c>
     </row>
     <row r="1086" spans="1:4">
@@ -16782,7 +16782,7 @@
         <v>304</v>
       </c>
       <c r="D1086">
-        <v>100.103033619565</v>
+        <v>-0.624029896061112</v>
       </c>
     </row>
     <row r="1087" spans="1:4">
@@ -16796,7 +16796,7 @@
         <v>305</v>
       </c>
       <c r="D1087">
-        <v>99.97733235176079</v>
+        <v>-0.492605041705924</v>
       </c>
     </row>
     <row r="1088" spans="1:4">
@@ -16810,7 +16810,7 @@
         <v>306</v>
       </c>
       <c r="D1088">
-        <v>99.491082642686</v>
+        <v>-2.22540993316464</v>
       </c>
     </row>
     <row r="1089" spans="1:4">
@@ -16824,7 +16824,7 @@
         <v>307</v>
       </c>
       <c r="D1089">
-        <v>99.49421925153131</v>
+        <v>-3.53148277205967</v>
       </c>
     </row>
     <row r="1090" spans="1:4">
@@ -16838,7 +16838,7 @@
         <v>308</v>
       </c>
       <c r="D1090">
-        <v>102.651940476089</v>
+        <v>-0.18111508934143</v>
       </c>
     </row>
     <row r="1091" spans="1:4">
@@ -16852,7 +16852,7 @@
         <v>309</v>
       </c>
       <c r="D1091">
-        <v>100.434298894287</v>
+        <v>-0.448329840236811</v>
       </c>
     </row>
     <row r="1092" spans="1:4">
@@ -16866,7 +16866,7 @@
         <v>310</v>
       </c>
       <c r="D1092">
-        <v>101.553253327191</v>
+        <v>2.10179933195925</v>
       </c>
     </row>
     <row r="1093" spans="1:4">
@@ -16880,7 +16880,7 @@
         <v>311</v>
       </c>
       <c r="D1093">
-        <v>102.027159454144</v>
+        <v>1.59477647430073</v>
       </c>
     </row>
     <row r="1094" spans="1:4">
@@ -16894,7 +16894,7 @@
         <v>312</v>
       </c>
       <c r="D1094">
-        <v>100.138750386422</v>
+        <v>2.93936577946524</v>
       </c>
     </row>
     <row r="1095" spans="1:4">
@@ -16908,7 +16908,7 @@
         <v>313</v>
       </c>
       <c r="D1095">
-        <v>102.256217093888</v>
+        <v>2.62023418961858</v>
       </c>
     </row>
     <row r="1096" spans="1:4">
@@ -16922,7 +16922,7 @@
         <v>314</v>
       </c>
       <c r="D1096">
-        <v>101.893346319552</v>
+        <v>1.40156843433387</v>
       </c>
     </row>
     <row r="1097" spans="1:4">
@@ -16936,7 +16936,7 @@
         <v>315</v>
       </c>
       <c r="D1097">
-        <v>102.557256983332</v>
+        <v>3.40639226929062</v>
       </c>
     </row>
     <row r="1098" spans="1:4">
@@ -16950,7 +16950,7 @@
         <v>316</v>
       </c>
       <c r="D1098">
-        <v>98.7211523688338</v>
+        <v>-1.38045891394555</v>
       </c>
     </row>
     <row r="1099" spans="1:4">
@@ -16964,7 +16964,7 @@
         <v>317</v>
       </c>
       <c r="D1099">
-        <v>101.689189299815</v>
+        <v>1.71224507374451</v>
       </c>
     </row>
     <row r="1100" spans="1:4">
@@ -16978,7 +16978,7 @@
         <v>318</v>
       </c>
       <c r="D1100">
-        <v>102.031739978812</v>
+        <v>2.55365332112282</v>
       </c>
     </row>
     <row r="1101" spans="1:4">
@@ -16992,7 +16992,7 @@
         <v>319</v>
       </c>
       <c r="D1101">
-        <v>95.92602869193939</v>
+        <v>-3.58632952390045</v>
       </c>
     </row>
     <row r="1102" spans="1:4">
@@ -17006,7 +17006,7 @@
         <v>320</v>
       </c>
       <c r="D1102">
-        <v>94.7580354041567</v>
+        <v>-7.68997160240828</v>
       </c>
     </row>
     <row r="1103" spans="1:4">
@@ -17020,7 +17020,7 @@
         <v>321</v>
       </c>
       <c r="D1103">
-        <v>99.18795255047181</v>
+        <v>-1.24095688179896</v>
       </c>
     </row>
     <row r="1104" spans="1:4">
@@ -17034,7 +17034,7 @@
         <v>322</v>
       </c>
       <c r="D1104">
-        <v>98.428087497691</v>
+        <v>-3.07736653146024</v>
       </c>
     </row>
     <row r="1105" spans="1:4">
@@ -17048,7 +17048,7 @@
         <v>323</v>
       </c>
       <c r="D1105">
-        <v>96.7082233282089</v>
+        <v>-5.2132551316649</v>
       </c>
     </row>
     <row r="1106" spans="1:4">
@@ -17062,7 +17062,7 @@
         <v>324</v>
       </c>
       <c r="D1106">
-        <v>98.0181821850643</v>
+        <v>-2.11762998157527</v>
       </c>
     </row>
     <row r="1107" spans="1:4">
@@ -17076,7 +17076,7 @@
         <v>325</v>
       </c>
       <c r="D1107">
-        <v>95.0310077297393</v>
+        <v>-7.06578980671148</v>
       </c>
     </row>
     <row r="1108" spans="1:4">
@@ -17090,7 +17090,7 @@
         <v>326</v>
       </c>
       <c r="D1108">
-        <v>95.4986125816627</v>
+        <v>-6.27590904496796</v>
       </c>
     </row>
     <row r="1109" spans="1:4">
@@ -17104,7 +17104,7 @@
         <v>327</v>
       </c>
       <c r="D1109">
-        <v>94.37648652134951</v>
+        <v>-7.97678360616846</v>
       </c>
     </row>
     <row r="1110" spans="1:4">
@@ -17118,7 +17118,7 @@
         <v>328</v>
       </c>
       <c r="D1110">
-        <v>94.9510392502594</v>
+        <v>-3.81895169182063</v>
       </c>
     </row>
     <row r="1111" spans="1:4">
@@ -17132,7 +17132,7 @@
         <v>329</v>
       </c>
       <c r="D1111">
-        <v>93.8051866318776</v>
+        <v>-7.75303916003561</v>
       </c>
     </row>
     <row r="1112" spans="1:4">
@@ -17146,7 +17146,7 @@
         <v>330</v>
       </c>
       <c r="D1112">
-        <v>94.0858915816832</v>
+        <v>-7.78762412439388</v>
       </c>
     </row>
     <row r="1113" spans="1:4">
@@ -17160,7 +17160,7 @@
         <v>331</v>
       </c>
       <c r="D1113">
-        <v>94.41092359870601</v>
+        <v>-1.57945149392044</v>
       </c>
     </row>
     <row r="1114" spans="1:4">
@@ -17174,7 +17174,7 @@
         <v>332</v>
       </c>
       <c r="D1114">
-        <v>92.7522887229693</v>
+        <v>-2.11670353087483</v>
       </c>
     </row>
     <row r="1115" spans="1:4">
@@ -17188,7 +17188,7 @@
         <v>333</v>
       </c>
       <c r="D1115">
-        <v>91.9180733469058</v>
+        <v>-7.32939738812204</v>
       </c>
     </row>
     <row r="1116" spans="1:4">
@@ -17202,7 +17202,7 @@
         <v>334</v>
       </c>
       <c r="D1116">
-        <v>89.5000664431293</v>
+        <v>-9.07060299710805</v>
       </c>
     </row>
     <row r="1117" spans="1:4">
@@ -17216,7 +17216,7 @@
         <v>335</v>
       </c>
       <c r="D1117">
-        <v>86.8435994688077</v>
+        <v>-10.2003981873626</v>
       </c>
     </row>
     <row r="1118" spans="1:4">
@@ -17230,7 +17230,7 @@
         <v>336</v>
       </c>
       <c r="D1118">
-        <v>60.7494488886383</v>
+        <v>-38.0222653242644</v>
       </c>
     </row>
     <row r="1119" spans="1:4">
@@ -17244,7 +17244,7 @@
         <v>337</v>
       </c>
       <c r="D1119">
-        <v>59.858956615042</v>
+        <v>-37.0111313716927</v>
       </c>
     </row>
     <row r="1120" spans="1:4">
@@ -17258,7 +17258,7 @@
         <v>338</v>
       </c>
       <c r="D1120">
-        <v>73.0080698035904</v>
+        <v>-23.5506487163258</v>
       </c>
     </row>
     <row r="1121" spans="1:4">
@@ -17272,7 +17272,7 @@
         <v>339</v>
       </c>
       <c r="D1121">
-        <v>74.8771783095351</v>
+        <v>-20.661193196044</v>
       </c>
     </row>
     <row r="1122" spans="1:4">
@@ -17286,7 +17286,7 @@
         <v>340</v>
       </c>
       <c r="D1122">
-        <v>77.5241003266011</v>
+        <v>-18.3536052488343</v>
       </c>
     </row>
     <row r="1123" spans="1:4">
@@ -17300,7 +17300,7 @@
         <v>341</v>
       </c>
       <c r="D1123">
-        <v>79.7880575721429</v>
+        <v>-14.9428081356978</v>
       </c>
     </row>
     <row r="1124" spans="1:4">
@@ -17314,7 +17314,7 @@
         <v>342</v>
       </c>
       <c r="D1124">
-        <v>80.5986523324478</v>
+        <v>-14.3350283687604</v>
       </c>
     </row>
     <row r="1125" spans="1:4">
@@ -17328,7 +17328,7 @@
         <v>343</v>
       </c>
       <c r="D1125">
-        <v>85.5651749843973</v>
+        <v>-9.369412221733571</v>
       </c>
     </row>
     <row r="1126" spans="1:4">
@@ -17342,7 +17342,7 @@
         <v>344</v>
       </c>
       <c r="D1126">
-        <v>82.81133642439551</v>
+        <v>-10.7177433952765</v>
       </c>
     </row>
     <row r="1127" spans="1:4">
@@ -17356,7 +17356,7 @@
         <v>345</v>
       </c>
       <c r="D1127">
-        <v>83.6671920505089</v>
+        <v>-8.976342732138701</v>
       </c>
     </row>
     <row r="1128" spans="1:4">
@@ -17370,7 +17370,7 @@
         <v>346</v>
       </c>
       <c r="D1128">
-        <v>85.7724747104677</v>
+        <v>-4.16490387192081</v>
       </c>
     </row>
     <row r="1129" spans="1:4">
@@ -17384,7 +17384,7 @@
         <v>347</v>
       </c>
       <c r="D1129">
-        <v>87.511092845807</v>
+        <v>0.768615512348785</v>
       </c>
     </row>
     <row r="1130" spans="1:4">
@@ -17398,7 +17398,7 @@
         <v>348</v>
       </c>
       <c r="D1130">
-        <v>87.4644464922859</v>
+        <v>43.9757036357971</v>
       </c>
     </row>
     <row r="1131" spans="1:4">
@@ -17412,7 +17412,7 @@
         <v>349</v>
       </c>
       <c r="D1131">
-        <v>86.9249755780383</v>
+        <v>45.2163226583787</v>
       </c>
     </row>
     <row r="1132" spans="1:4">
@@ -17426,7 +17426,7 @@
         <v>350</v>
       </c>
       <c r="D1132">
-        <v>84.14686474967149</v>
+        <v>15.2569366318644</v>
       </c>
     </row>
     <row r="1133" spans="1:4">
@@ -17440,7 +17440,7 @@
         <v>351</v>
       </c>
       <c r="D1133">
-        <v>87.1068525316998</v>
+        <v>16.3329795516711</v>
       </c>
     </row>
     <row r="1134" spans="1:4">
@@ -17454,7 +17454,7 @@
         <v>352</v>
       </c>
       <c r="D1134">
-        <v>88.33118128990741</v>
+        <v>13.9402855599448</v>
       </c>
     </row>
     <row r="1135" spans="1:4">
@@ -17468,7 +17468,7 @@
         <v>353</v>
       </c>
       <c r="D1135">
-        <v>87.7811665509124</v>
+        <v>10.0179265193194</v>
       </c>
     </row>
     <row r="1136" spans="1:4">
@@ -17482,7 +17482,7 @@
         <v>354</v>
       </c>
       <c r="D1136">
-        <v>87.8833723107432</v>
+        <v>9.038265240773359</v>
       </c>
     </row>
     <row r="1137" spans="1:4">
@@ -17496,7 +17496,7 @@
         <v>355</v>
       </c>
       <c r="D1137">
-        <v>88.6190354330009</v>
+        <v>3.56904599232161</v>
       </c>
     </row>
     <row r="1138" spans="1:4">
@@ -17510,7 +17510,7 @@
         <v>356</v>
       </c>
       <c r="D1138">
-        <v>88.7114093280674</v>
+        <v>7.12471644393579</v>
       </c>
     </row>
     <row r="1139" spans="1:4">
@@ -17524,7 +17524,7 @@
         <v>357</v>
       </c>
       <c r="D1139">
-        <v>91.42902066842611</v>
+        <v>9.27702774252479</v>
       </c>
     </row>
     <row r="1140" spans="1:4">
@@ -17538,7 +17538,7 @@
         <v>358</v>
       </c>
       <c r="D1140">
-        <v>91.2752293900522</v>
+        <v>6.41552514155563</v>
       </c>
     </row>
     <row r="1141" spans="1:4">
@@ -17552,7 +17552,7 @@
         <v>359</v>
       </c>
       <c r="D1141">
-        <v>94.4438949883131</v>
+        <v>7.92219810889755</v>
       </c>
     </row>
     <row r="1142" spans="1:4">
@@ -17566,7 +17566,7 @@
         <v>360</v>
       </c>
       <c r="D1142">
-        <v>94.52173966184949</v>
+        <v>8.06875645201279</v>
       </c>
     </row>
     <row r="1143" spans="1:4">
@@ -17580,7 +17580,7 @@
         <v>361</v>
       </c>
       <c r="D1143">
-        <v>93.58529069491691</v>
+        <v>7.66214206284039</v>
       </c>
     </row>
     <row r="1144" spans="1:4">
@@ -17594,7 +17594,7 @@
         <v>362</v>
       </c>
       <c r="D1144">
-        <v>93.0083763424597</v>
+        <v>10.5310062581064</v>
       </c>
     </row>
     <row r="1145" spans="1:4">
@@ -17608,7 +17608,7 @@
         <v>363</v>
       </c>
       <c r="D1145">
-        <v>92.02676626370879</v>
+        <v>5.64813627058623</v>
       </c>
     </row>
     <row r="1146" spans="1:4">
@@ -17622,7 +17622,7 @@
         <v>364</v>
       </c>
       <c r="D1146">
-        <v>94.19648942906031</v>
+        <v>6.64013325023093</v>
       </c>
     </row>
     <row r="1147" spans="1:4">
@@ -17636,7 +17636,7 @@
         <v>365</v>
       </c>
       <c r="D1147">
-        <v>93.64683034015459</v>
+        <v>6.68214381252287</v>
       </c>
     </row>
     <row r="1148" spans="1:4">
@@ -17650,7 +17650,7 @@
         <v>366</v>
       </c>
       <c r="D1148">
-        <v>94.4733795425084</v>
+        <v>7.49858256288102</v>
       </c>
     </row>
     <row r="1149" spans="1:4">
@@ -17664,7 +17664,7 @@
         <v>367</v>
       </c>
       <c r="D1149">
-        <v>96.4534780838857</v>
+        <v>8.840586689535691</v>
       </c>
     </row>
     <row r="1150" spans="1:4">
@@ -17678,7 +17678,7 @@
         <v>368</v>
       </c>
       <c r="D1150">
-        <v>99.9897916311664</v>
+        <v>12.7135645668641</v>
       </c>
     </row>
     <row r="1151" spans="1:4">
@@ -17692,7 +17692,7 @@
         <v>369</v>
       </c>
       <c r="D1151">
-        <v>100.537245946087</v>
+        <v>9.962072448191829</v>
       </c>
     </row>
     <row r="1152" spans="1:4">
@@ -17706,7 +17706,7 @@
         <v>370</v>
       </c>
       <c r="D1152">
-        <v>102.20549817384</v>
+        <v>11.9750658057278</v>
       </c>
     </row>
     <row r="1153" spans="1:4">
@@ -17720,7 +17720,7 @@
         <v>371</v>
       </c>
       <c r="D1153">
-        <v>102.584986503931</v>
+        <v>8.620029401186089</v>
       </c>
     </row>
     <row r="1154" spans="1:4">
@@ -17734,7 +17734,7 @@
         <v>372</v>
       </c>
       <c r="D1154">
-        <v>102.761298962498</v>
+        <v>8.71710500687508</v>
       </c>
     </row>
     <row r="1155" spans="1:4">
@@ -17748,7 +17748,7 @@
         <v>373</v>
       </c>
       <c r="D1155">
-        <v>105.9531400926</v>
+        <v>13.2155911531029</v>
       </c>
     </row>
     <row r="1156" spans="1:4">
@@ -17762,7 +17762,7 @@
         <v>374</v>
       </c>
       <c r="D1156">
-        <v>108.390931746722</v>
+        <v>16.5388925268658</v>
       </c>
     </row>
     <row r="1157" spans="1:4">
@@ -17776,7 +17776,7 @@
         <v>375</v>
       </c>
       <c r="D1157">
-        <v>106.333808618031</v>
+        <v>15.5466098996942</v>
       </c>
     </row>
     <row r="1158" spans="1:4">
@@ -17790,7 +17790,7 @@
         <v>376</v>
       </c>
       <c r="D1158">
-        <v>108.207807159048</v>
+        <v>14.8745646625607</v>
       </c>
     </row>
     <row r="1159" spans="1:4">
@@ -17804,7 +17804,7 @@
         <v>377</v>
       </c>
       <c r="D1159">
-        <v>111.22575491996</v>
+        <v>18.7715104888796</v>
       </c>
     </row>
     <row r="1160" spans="1:4">
@@ -17818,7 +17818,7 @@
         <v>378</v>
       </c>
       <c r="D1160">
-        <v>113.126108555062</v>
+        <v>19.7438993956608</v>
       </c>
     </row>
     <row r="1161" spans="1:4">
@@ -17832,7 +17832,7 @@
         <v>379</v>
       </c>
       <c r="D1161">
-        <v>110.213484168466</v>
+        <v>14.2659511693432</v>
       </c>
     </row>
     <row r="1162" spans="1:4">
@@ -17846,7 +17846,7 @@
         <v>380</v>
       </c>
       <c r="D1162">
-        <v>111.676083241244</v>
+        <v>11.6874847116243</v>
       </c>
     </row>
     <row r="1163" spans="1:4">
@@ -17860,7 +17860,7 @@
         <v>381</v>
       </c>
       <c r="D1163">
-        <v>112.514648107718</v>
+        <v>11.9133979142952</v>
       </c>
     </row>
     <row r="1164" spans="1:4">
@@ -17874,7 +17874,7 @@
         <v>382</v>
       </c>
       <c r="D1164">
-        <v>112.369743853975</v>
+        <v>9.944910852884609</v>
       </c>
     </row>
     <row r="1165" spans="1:4">
@@ -17888,7 +17888,7 @@
         <v>383</v>
       </c>
       <c r="D1165">
-        <v>111.688718943294</v>
+        <v>8.87433215094701</v>
       </c>
     </row>
     <row r="1166" spans="1:4">
@@ -17902,7 +17902,7 @@
         <v>384</v>
       </c>
       <c r="D1166">
-        <v>112.16492091391</v>
+        <v>9.15093721698066</v>
       </c>
     </row>
     <row r="1167" spans="1:4">
@@ -17916,7 +17916,7 @@
         <v>385</v>
       </c>
       <c r="D1167">
-        <v>111.747609887886</v>
+        <v>5.46889860009982</v>
       </c>
     </row>
     <row r="1168" spans="1:4">
@@ -17930,7 +17930,7 @@
         <v>386</v>
       </c>
       <c r="D1168">
-        <v>111.008176917084</v>
+        <v>2.41463481140446</v>
       </c>
     </row>
     <row r="1169" spans="1:4">
@@ -17944,7 +17944,7 @@
         <v>387</v>
       </c>
       <c r="D1169">
-        <v>113.515006963471</v>
+        <v>6.75344788150688</v>
       </c>
     </row>
     <row r="1170" spans="1:4">
@@ -17958,7 +17958,7 @@
         <v>388</v>
       </c>
       <c r="D1170">
-        <v>112.468487852147</v>
+        <v>3.93749841620623</v>
       </c>
     </row>
     <row r="1171" spans="1:4">
@@ -17972,7 +17972,7 @@
         <v>389</v>
       </c>
       <c r="D1171">
-        <v>110.977677532919</v>
+        <v>-0.223039517438667</v>
       </c>
     </row>
     <row r="1172" spans="1:4">
@@ -17986,7 +17986,7 @@
         <v>390</v>
       </c>
       <c r="D1172">
-        <v>109.312453682876</v>
+        <v>-3.37115359212571</v>
       </c>
     </row>
     <row r="1173" spans="1:4">
@@ -18000,7 +18000,7 @@
         <v>391</v>
       </c>
       <c r="D1173">
-        <v>109.804093226229</v>
+        <v>-0.37145268142619</v>
       </c>
     </row>
     <row r="1174" spans="1:4">
@@ -18014,7 +18014,7 @@
         <v>392</v>
       </c>
       <c r="D1174">
-        <v>106.088902279142</v>
+        <v>-5.00302374505068</v>
       </c>
     </row>
     <row r="1175" spans="1:4">
@@ -18028,7 +18028,7 @@
         <v>393</v>
       </c>
       <c r="D1175">
-        <v>105.195903711918</v>
+        <v>-6.50470362649427</v>
       </c>
     </row>
     <row r="1176" spans="1:4">
@@ -18042,7 +18042,7 @@
         <v>394</v>
       </c>
       <c r="D1176">
-        <v>105.944616305446</v>
+        <v>-5.71784479359362</v>
       </c>
     </row>
     <row r="1177" spans="1:4">
@@ -18056,7 +18056,7 @@
         <v>395</v>
       </c>
       <c r="D1177">
-        <v>106.090335958617</v>
+        <v>-5.01248741828562</v>
       </c>
     </row>
     <row r="1178" spans="1:4">
@@ -18070,7 +18070,7 @@
         <v>396</v>
       </c>
       <c r="D1178">
-        <v>102.189985989532</v>
+        <v>-8.893096739250639</v>
       </c>
     </row>
     <row r="1179" spans="1:4">
@@ -18084,7 +18084,7 @@
         <v>397</v>
       </c>
       <c r="D1179">
-        <v>104.554053530988</v>
+        <v>-6.43732457823048</v>
       </c>
     </row>
     <row r="1180" spans="1:4">
@@ -18098,7 +18098,7 @@
         <v>398</v>
       </c>
       <c r="D1180">
-        <v>102.973796801404</v>
+        <v>-7.23764711646527</v>
       </c>
     </row>
     <row r="1181" spans="1:4">
@@ -18112,7 +18112,7 @@
         <v>399</v>
       </c>
       <c r="D1181">
-        <v>104.841033924209</v>
+        <v>-7.64125666842735</v>
       </c>
     </row>
     <row r="1182" spans="1:4">
@@ -18126,7 +18126,7 @@
         <v>400</v>
       </c>
       <c r="D1182">
-        <v>101.927441736061</v>
+        <v>-9.37244406623787</v>
       </c>
     </row>
     <row r="1183" spans="1:4">
@@ -18140,7 +18140,7 @@
         <v>401</v>
       </c>
       <c r="D1183">
-        <v>102.032181423291</v>
+        <v>-8.0606265228199</v>
       </c>
     </row>
     <row r="1184" spans="1:4">
@@ -18154,7 +18154,7 @@
         <v>402</v>
       </c>
       <c r="D1184">
-        <v>103.029078276178</v>
+        <v>-5.7480874273727</v>
       </c>
     </row>
     <row r="1185" spans="1:4">
@@ -18168,7 +18168,7 @@
         <v>403</v>
       </c>
       <c r="D1185">
-        <v>103.607716363962</v>
+        <v>-5.64312010618823</v>
       </c>
     </row>
     <row r="1186" spans="1:4">
@@ -18182,7 +18182,7 @@
         <v>404</v>
       </c>
       <c r="D1186">
-        <v>104.057114158663</v>
+        <v>-1.91517498704337</v>
       </c>
     </row>
     <row r="1187" spans="1:4">
@@ -18196,7 +18196,7 @@
         <v>405</v>
       </c>
       <c r="D1187">
-        <v>103.024273372109</v>
+        <v>-2.06436777781394</v>
       </c>
     </row>
     <row r="1188" spans="1:4">
@@ -18210,7 +18210,7 @@
         <v>406</v>
       </c>
       <c r="D1188">
-        <v>102.655046964434</v>
+        <v>-3.10498962167925</v>
       </c>
     </row>
     <row r="1189" spans="1:4">
@@ -18224,7 +18224,7 @@
         <v>407</v>
       </c>
       <c r="D1189">
-        <v>103.25572286561</v>
+        <v>-2.67188624429723</v>
       </c>
     </row>
     <row r="1190" spans="1:4">
@@ -18238,7 +18238,7 @@
         <v>408</v>
       </c>
       <c r="D1190">
-        <v>107.517187426567</v>
+        <v>5.21303666445429</v>
       </c>
     </row>
     <row r="1191" spans="1:4">
@@ -18252,7 +18252,7 @@
         <v>409</v>
       </c>
       <c r="D1191">
-        <v>107.080851092967</v>
+        <v>2.41673801889479</v>
       </c>
     </row>
   </sheetData>
